--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>99</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5186</v>
+        <v>7019</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4258</v>
+        <v>5683</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3190</v>
+        <v>4364</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>02151</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SARONNO</t>
+          <t>AGRATE BRIANZA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -817,35 +817,35 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>218</v>
+        <v>309</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>285</v>
+        <v>405</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>230</v>
+        <v>620</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02151</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AGRATE BRIANZA</t>
+          <t>SARONNO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>256</v>
+        <v>41</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>153</v>
+        <v>257</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>464</v>
+        <v>314</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>02308</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>147</v>
+        <v>322</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02308</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>86</v>
+        <v>195</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>186</v>
+        <v>322</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1355,49 +1355,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PODESTÀ ANDREA</t>
+        </is>
+      </c>
       <c r="E21" s="12" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1407,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1465,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1500,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1515,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1554,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1569,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>185</v>
+        <v>255</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1608,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1623,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>194</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="H26" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1677,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>102</v>
+        <v>274</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>116</v>
+        <v>302</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1735,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1770,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1785,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>41</v>
+        <v>229</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1878,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1893,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1932,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1945,37 +1949,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>RAVA CLAUDIO</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="12" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>170</v>
+        <v>301</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2005,47 +2005,47 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,31 +2059,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2094,12 +2094,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,35 +2109,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2148,12 +2148,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,39 +2163,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2221,47 +2221,47 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="I37" s="12" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,46 +2271,46 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>65</v>
-      </c>
       <c r="H38" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2325,35 +2325,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>56</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>11</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,51 +2379,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,35 +2433,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F41" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2472,12 +2472,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2487,35 +2487,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2526,12 +2526,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,35 +2541,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2580,12 +2580,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,35 +2595,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G44" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2634,12 +2634,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,35 +2649,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L45" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>90</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2688,12 +2688,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,51 +2703,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2757,39 +2757,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2815,31 +2815,31 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J48" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K48" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K48" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L48" s="12" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2869,31 +2869,31 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2919,35 +2919,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2958,12 +2958,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2973,51 +2973,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3027,51 +3027,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3081,51 +3081,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="J53" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="M53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K53" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3135,51 +3135,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>52</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3189,51 +3189,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J55" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3243,51 +3243,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3297,51 +3297,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J57" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="M57" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3351,51 +3351,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3405,51 +3405,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3459,51 +3459,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3513,51 +3513,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K61" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L61" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3567,51 +3567,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3621,51 +3621,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3675,51 +3675,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I64" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J64" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J64" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="K64" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3729,51 +3729,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H65" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K65" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L65" s="12" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3783,46 +3783,46 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3841,31 +3841,31 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3876,12 +3876,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,47 +3895,47 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>30</v>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3945,51 +3945,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3999,51 +3999,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4053,35 +4053,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4111,47 +4111,47 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4161,51 +4161,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4215,51 +4215,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,47 +4273,47 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4323,51 +4323,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4377,51 +4377,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>22</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4431,35 +4431,35 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J78" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K78" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4489,31 +4489,31 @@
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4524,12 +4524,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4539,51 +4539,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J80" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="M80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4593,11 +4593,11 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
@@ -4609,16 +4609,16 @@
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
@@ -4632,12 +4632,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4647,35 +4647,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G82" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="M82" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4686,12 +4686,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4701,35 +4701,35 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J83" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4755,32 +4755,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
@@ -4794,12 +4794,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4809,35 +4809,35 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4848,12 +4848,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4863,51 +4863,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,47 +4921,47 @@
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4971,51 +4971,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5025,51 +5025,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5079,26 +5079,26 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>0</v>
@@ -5137,31 +5137,31 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H91" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I91" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="I91" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="M91" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="L91" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M91" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5172,12 +5172,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>01858</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>BREGNANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5185,49 +5185,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>DELLERBA ALBERTO</t>
+        </is>
+      </c>
       <c r="E92" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F92" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="G92" s="12" t="n">
+      <c r="H92" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H92" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00607</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5235,49 +5239,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
       <c r="E93" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="M93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5287,51 +5295,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G94" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H94" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>01923</t>
+          <t>01858</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CANTÙ</t>
+          <t>BREGNANO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5339,53 +5347,49 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>RAVA CLAUDIO</t>
-        </is>
-      </c>
+      <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="I95" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J95" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J95" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K95" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5395,51 +5399,51 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G96" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H96" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="J96" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>00607</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5447,37 +5451,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>BIANCHI ENRICO</t>
-        </is>
-      </c>
+      <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J97" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M97" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5488,12 +5488,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5503,39 +5503,39 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J99" s="12" t="n">
         <v>0</v>
@@ -5582,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -5596,12 +5596,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>01923</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>CANTÙ</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5611,51 +5611,51 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G100" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K100" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="M100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5665,51 +5665,51 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F101" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G101" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G101" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="H101" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J101" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5719,51 +5719,51 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="I102" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J102" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="K102" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K102" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L102" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M102" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>00425</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5773,51 +5773,51 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>00753</t>
+          <t>00425</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>ORBASSANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5827,20 +5827,20 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I104" s="12" t="n">
         <v>0</v>
@@ -5866,12 +5866,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>00753</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>ORBASSANO</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5881,20 +5881,20 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I105" s="12" t="n">
         <v>0</v>
@@ -5942,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>
@@ -5996,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="I107" s="12" t="n">
         <v>0</v>
@@ -6050,13 +6050,13 @@
         <v>0</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I108" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>620</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.07903225806451612</v>
+        <v>49</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>314</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.1082802547770701</v>
+        <v>34</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>320</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.778125</v>
+        <v>249</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>228</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.03947368421052631</v>
+        <v>9</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>303</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.1188118811881188</v>
+        <v>36</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>178</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.651685393258427</v>
+        <v>116</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>186</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.09677419354838709</v>
+        <v>18</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>322</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.03105590062111801</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>119</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5966386554621849</v>
+        <v>71</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>322</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.04968944099378882</v>
+        <v>16</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>73</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.6575342465753424</v>
+        <v>48</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>184</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.3043478260869565</v>
+        <v>56</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>173</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.3005780346820809</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>284</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.0352112676056338</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>236</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.0423728813559322</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>241</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.04149377593360996</v>
+        <v>10</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>302</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.04304635761589404</v>
+        <v>13</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>215</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.05116279069767442</v>
+        <v>11</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>145</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.2689655172413793</v>
+        <v>39</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>162</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.1851851851851852</v>
+        <v>30</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>176</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.2102272727272727</v>
+        <v>37</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>161</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.04347826086956522</v>
+        <v>7</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>173</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.138728323699422</v>
+        <v>24</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>279</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.1612903225806452</v>
+        <v>45</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>243</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.2716049382716049</v>
+        <v>66</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>212</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.169811320754717</v>
+        <v>36</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>90</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.2222222222222222</v>
+        <v>20</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.09302325581395349</v>
+        <v>12</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>176</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.3181818181818182</v>
+        <v>56</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>169</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>124</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.8629032258064516</v>
+        <v>107</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>188</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.02659574468085106</v>
+        <v>5</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>198</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.04040404040404041</v>
+        <v>8</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>63</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.4126984126984127</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>64</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.109375</v>
+        <v>7</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>78</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.05128205128205128</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>159</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.1006289308176101</v>
+        <v>16</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>145</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0.1310344827586207</v>
+        <v>19</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>92</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.108695652173913</v>
+        <v>10</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>81</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.06172839506172839</v>
+        <v>5</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>63</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.03174603174603174</v>
+        <v>2</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>155</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.08387096774193549</v>
+        <v>13</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>146</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0.03424657534246575</v>
+        <v>5</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>96</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0.21875</v>
+        <v>21</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>77</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0.3766233766233766</v>
+        <v>29</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>57</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.3859649122807017</v>
+        <v>22</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>123</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0.1219512195121951</v>
+        <v>15</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>40</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0.65</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>67</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0.07462686567164178</v>
+        <v>5</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>17</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0.1764705882352941</v>
+        <v>3</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>139</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>78</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0.2564102564102564</v>
+        <v>20</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>96</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0.34375</v>
+        <v>33</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>159</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0.0440251572327044</v>
+        <v>7</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>79</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0.0379746835443038</v>
+        <v>3</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>112</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.1696428571428572</v>
+        <v>19</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>110</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0.5363636363636364</v>
+        <v>59</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>14</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>1</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>98</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>7</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>101</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0.0297029702970297</v>
+        <v>3</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>112</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0.08035714285714286</v>
+        <v>9</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>64</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.28125</v>
+        <v>18</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>22</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.04545454545454546</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>48</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.6041666666666666</v>
+        <v>29</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>110</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>41</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.0975609756097561</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>98</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.06122448979591837</v>
+        <v>6</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>55</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.07272727272727272</v>
+        <v>4</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>75</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.01333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>34</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>1</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>31</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.06451612903225806</v>
+        <v>2</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.06666666666666667</v>
+        <v>3</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>60</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.2666666666666667</v>
+        <v>16</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>46</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.1739130434782609</v>
+        <v>8</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>58</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.05172413793103448</v>
+        <v>3</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>8</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>25</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>33</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.09090909090909091</v>
+        <v>3</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>16</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>23</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.391304347826087</v>
+        <v>9</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>7</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.2857142857142857</v>
+        <v>2</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>99</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7019</v>
+        <v>7446</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5683</v>
+        <v>6016</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4364</v>
+        <v>4678</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>620</v>
+        <v>663</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02862</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASSANO MAGNAGO</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02862</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>CASSANO MAGNAGO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>303</v>
+        <v>241</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>279</v>
+        <v>377</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>178</v>
+        <v>327</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>18</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>66</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>2</v>
@@ -1319,16 +1319,16 @@
         <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>16</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="I24" s="12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>236</v>
+        <v>308</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>274</v>
+        <v>166</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>302</v>
+        <v>153</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>188</v>
+        <v>292</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>215</v>
+        <v>333</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>231</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1949,49 +1949,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>BIANCHI ENRICO</t>
+        </is>
+      </c>
       <c r="E32" s="12" t="n">
         <v>130</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>301</v>
+        <v>121</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>182</v>
+        <v>36</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>473</v>
+        <v>9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1999,41 +2003,37 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>BIANCHI ENRICO</t>
-        </is>
-      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="12" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>114</v>
+        <v>316</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>506</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2059,47 +2059,47 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,35 +2109,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>243</v>
+        <v>91</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2148,12 +2148,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,51 +2163,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2217,35 +2217,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2256,12 +2256,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2271,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,35 +2325,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>26</v>
@@ -2404,10 +2404,10 @@
         <v>28</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2437,35 +2437,35 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2491,19 +2491,19 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>69</v>
-      </c>
       <c r="H42" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>27</v>
@@ -2512,7 +2512,7 @@
         <v>8</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>5</v>
@@ -2526,12 +2526,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,51 +2541,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,39 +2595,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2653,47 +2653,47 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,47 +2707,47 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,47 +2761,47 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2811,51 +2811,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2865,51 +2865,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J49" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K49" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K49" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="L49" s="12" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2919,35 +2919,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G50" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J50" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H50" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>60</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>48</v>
@@ -2998,7 +2998,7 @@
         <v>15</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>2</v>
@@ -3012,12 +3012,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3027,51 +3027,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="G52" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="J52" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H52" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="K52" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3081,51 +3081,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3135,51 +3135,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K54" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3189,51 +3189,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3243,51 +3243,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3297,35 +3297,35 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="G57" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H57" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H57" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I57" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3336,12 +3336,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3351,39 +3351,39 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3409,35 +3409,35 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3463,47 +3463,47 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,47 +3517,47 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3567,39 +3567,39 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3625,28 +3625,28 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J63" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K63" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K63" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L63" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>33</v>
@@ -3660,12 +3660,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3675,35 +3675,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3714,12 +3714,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3729,51 +3729,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K65" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L65" s="12" t="n">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3783,51 +3783,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3837,51 +3837,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F67" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F67" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="G67" s="12" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3891,51 +3891,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F68" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J68" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3945,39 +3945,39 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I69" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="J69" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>2</v>
@@ -4015,19 +4015,19 @@
         <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J70" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M70" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4057,16 +4057,16 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>26</v>
@@ -4075,13 +4075,13 @@
         <v>5</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4092,12 +4092,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4107,51 +4107,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4161,35 +4161,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="12" t="n">
         <v>31</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>40</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4200,12 +4200,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4215,35 +4215,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4254,12 +4254,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4269,51 +4269,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4323,35 +4323,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4362,12 +4362,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4377,35 +4377,35 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F77" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I77" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G77" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J77" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4416,12 +4416,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4431,51 +4431,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4485,32 +4485,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>4</v>
@@ -4524,12 +4524,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4539,35 +4539,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4597,19 +4597,19 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>6</v>
@@ -4618,14 +4618,14 @@
         <v>4</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4651,31 +4651,31 @@
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4686,12 +4686,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4701,51 +4701,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4755,39 +4755,39 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4813,19 +4813,19 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="G85" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>6</v>
@@ -4834,14 +4834,14 @@
         <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4867,19 +4867,19 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F86" s="12" t="n">
         <v>41</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>6</v>
@@ -4888,10 +4888,10 @@
         <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4902,12 +4902,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4917,51 +4917,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L87" s="12" t="n">
-        <v>60</v>
-      </c>
       <c r="M87" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4971,51 +4971,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J88" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K88" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L88" s="12" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,31 +5029,31 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5064,12 +5064,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5079,51 +5079,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J90" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5133,39 +5133,39 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5191,28 +5191,28 @@
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H92" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>1</v>
@@ -5226,12 +5226,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5241,23 +5241,23 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G93" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="H93" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J93" s="12" t="n">
         <v>3</v>
@@ -5266,14 +5266,14 @@
         <v>0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F94" s="12" t="n">
         <v>38</v>
@@ -5311,16 +5311,16 @@
         <v>5</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>2</v>
@@ -5334,12 +5334,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>01858</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>BREGNANO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5347,37 +5347,41 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
       <c r="E95" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I95" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J95" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K95" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5403,19 +5407,19 @@
         </is>
       </c>
       <c r="E96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="J96" s="12" t="n">
         <v>0</v>
@@ -5438,12 +5442,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>00607</t>
+          <t>01858</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>BREGNANO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5453,31 +5457,31 @@
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K97" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I97" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L97" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5488,12 +5492,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00607</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5501,41 +5505,37 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>DELLI CARRI LUCA</t>
-        </is>
-      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="12" t="n">
         <v>7</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J98" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M98" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H99" s="12" t="n">
         <v>0</v>
@@ -5618,13 +5618,13 @@
         <v>7</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G100" s="12" t="n">
         <v>47</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I100" s="12" t="n">
         <v>5</v>
@@ -5672,13 +5672,13 @@
         <v>6</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>6</v>
@@ -5690,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M101" s="12" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F102" s="12" t="n">
         <v>0</v>
@@ -5741,10 +5741,10 @@
         <v>3</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M102" s="12" t="n">
         <v>0</v>
@@ -5780,13 +5780,13 @@
         <v>2</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I103" s="12" t="n">
         <v>3</v>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>0</v>
@@ -5996,13 +5996,13 @@
         <v>0</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I107" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N109" headerRowCount="1">
-  <autoFilter ref="A10:N109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N99" headerRowCount="1">
+  <autoFilter ref="A10:N99"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7446</v>
+        <v>6974</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6016</v>
+        <v>5640</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4678</v>
+        <v>4360</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>334</v>
+        <v>251</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>251</v>
+        <v>179</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
         <v>162</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>333</v>
+        <v>188</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>10</v>
+        <v>231</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2003,49 +2003,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>DELLERBA ALBERTO</t>
+        </is>
+      </c>
       <c r="E33" s="12" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>316</v>
+        <v>121</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>182</v>
+        <v>51</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>506</v>
+        <v>43</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>202</v>
+        <v>93</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>292</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2217,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K37" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>229</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>38</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2256,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2364,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K41" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>129</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>111</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,47 +2495,47 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2634,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J45" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L45" s="12" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>170</v>
+        <v>87</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2742,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2757,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2811,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K48" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>97</v>
-      </c>
       <c r="M48" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2865,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2919,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K50" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>164</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L50" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2973,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,31 +3035,31 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3066,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3081,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3135,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K54" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L54" s="12" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3189,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>49</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3228,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3243,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,47 +3305,47 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3351,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3390,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3405,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3459,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>51</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3513,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3567,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3606,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3621,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3675,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G64" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F64" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G64" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="H64" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" s="12" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3714,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3729,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3783,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3837,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J67" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3876,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3891,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,47 +3953,47 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="J69" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="K69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="M69" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3999,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="I70" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K70" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J70" s="12" t="n">
+      <c r="L70" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="M70" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4038,7 +4042,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4057,31 +4061,31 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J71" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K71" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="L71" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4092,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4107,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4161,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4215,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4254,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4269,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>28</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4323,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4377,35 +4381,35 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4416,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4431,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4485,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F79" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F79" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="G79" s="12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J79" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4524,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4539,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4593,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4647,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4701,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J83" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K83" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4755,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4809,51 +4813,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4863,51 +4867,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4917,51 +4921,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="M87" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4971,51 +4975,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H88" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="J88" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5025,51 +5029,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J89" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L89" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5079,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G90" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J90" s="12" t="n">
+      <c r="M90" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K90" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5133,51 +5137,51 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G91" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I91" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="J91" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5187,51 +5191,51 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5241,23 +5245,23 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G93" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="J93" s="12" t="n">
         <v>3</v>
@@ -5266,26 +5270,26 @@
         <v>0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5295,51 +5299,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G94" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H94" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="J94" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5349,51 +5353,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5403,35 +5407,35 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K96" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -5442,12 +5446,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>01858</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>BREGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5455,30 +5459,34 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
       <c r="E97" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>0</v>
@@ -5492,12 +5500,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>00607</t>
+          <t>00753</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ORBASSANO</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5505,33 +5513,37 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>PODESTÀ ANDREA</t>
+        </is>
+      </c>
       <c r="E98" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K98" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -5542,12 +5554,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>VALMADRERA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5557,23 +5569,23 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J99" s="12" t="n">
         <v>0</v>
@@ -5582,552 +5594,12 @@
         <v>0</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>01923</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>CANTÙ</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>RAVA CLAUDIO</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>51654</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>SANTHIÀ</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>BIANCHI ENRICO</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>02925</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>CARDANO AL CAMPO</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>SALVINELLI LUCA</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>55827</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>TORINO</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>GUERRA GIUSEPPE</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>00425</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>NOVARA</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>BIANCHI ENRICO</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>00753</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>ORBASSANO</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>PODESTÀ ANDREA</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>51215</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>IVREA</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>DELLI CARRI LUCA</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>52082</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>PIACENZA</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>GIURICIN ANTONIO</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>52247</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>MILANO</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>RECCHIA ALESSANDRO</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>57111</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>VALMADRERA</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>ADINOLFI VINCENZO</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N99" headerRowCount="1">
-  <autoFilter ref="A10:N99"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N97" headerRowCount="1">
+  <autoFilter ref="A10:N97"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>6974</v>
@@ -5497,114 +5497,6 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>00753</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>ORBASSANO</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>PODESTÀ ANDREA</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>57111</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>VALMADRERA</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>ADINOLFI VINCENZO</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>87</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6974</v>
+        <v>7427</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5640</v>
+        <v>5976</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4360</v>
+        <v>4676</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>284</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>268</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="L12" s="12" t="n">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>9</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>141</v>
-      </c>
       <c r="G22" s="12" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>11</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="L26" s="12" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>45</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>236</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,39 +2275,39 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2333,19 +2333,19 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>27</v>
@@ -2354,10 +2354,10 @@
         <v>8</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>8</v>
@@ -2495,28 +2495,28 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>9</v>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2549,47 +2549,47 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2603,47 +2603,47 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J44" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K44" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,39 +2707,39 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>91</v>
@@ -2777,19 +2777,19 @@
         <v>5</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="H49" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="J49" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K49" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3035,31 +3035,31 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3089,28 +3089,28 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H53" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="J53" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>32</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,35 +3301,35 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F57" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G57" s="12" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,32 +3409,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>6</v>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H60" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L60" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="M60" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G64" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="J64" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K64" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>41</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,39 +3787,39 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3845,31 +3845,31 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4061,31 +4061,31 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4169,47 +4169,47 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4223,35 +4223,35 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4280,13 +4280,13 @@
         <v>32</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>28</v>
@@ -4298,7 +4298,7 @@
         <v>7</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>11</v>
@@ -4334,13 +4334,13 @@
         <v>31</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>22</v>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L78" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,39 +4489,39 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G79" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K79" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4547,47 +4547,47 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G82" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F82" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="H82" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L82" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4817,31 +4817,31 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G85" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="H85" s="12" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,51 +4867,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J86" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M86" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K86" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,51 +4921,51 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F87" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I87" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="J87" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,51 +4975,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,39 +5029,39 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J90" s="12" t="n">
         <v>2</v>
@@ -5122,12 +5122,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,35 +5137,35 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5176,12 +5176,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5284,12 +5284,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>0</v>
@@ -5318,16 +5318,16 @@
         <v>7</v>
       </c>
       <c r="J94" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M94" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M94" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5338,12 +5338,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,51 +5353,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5407,39 +5407,39 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F96" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L96" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5468,13 +5468,13 @@
         <v>2</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="I97" s="12" t="n">
         <v>3</v>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>87</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7427</v>
+        <v>7886</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5976</v>
+        <v>6349</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4676</v>
+        <v>4958</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>700</v>
+        <v>733</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>464</v>
+        <v>502</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="F13" s="12" t="n">
+        <v>299</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>277</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>371</v>
+      </c>
+      <c r="M13" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>263</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>356</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>275</v>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>55</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02862</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASSANO MAGNAGO</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>247</v>
+        <v>373</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02862</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>CASSANO MAGNAGO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>352</v>
+        <v>266</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J18" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K18" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="L18" s="12" t="n">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>15</v>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="I19" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>141</v>
-      </c>
       <c r="G21" s="12" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="K23" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>320</v>
+        <v>213</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>199</v>
+        <v>335</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>146</v>
+        <v>324</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>187</v>
+        <v>10</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>349</v>
+        <v>221</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1739,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K28" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>31</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>30</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>21</v>
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,39 +2113,39 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>197</v>
+        <v>282</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2171,35 +2171,35 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,31 +2225,31 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>37</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2279,28 +2279,28 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>12</v>
@@ -2333,19 +2333,19 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>27</v>
@@ -2354,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>6</v>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="L41" s="12" t="n">
-        <v>224</v>
+        <v>74</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="L45" s="12" t="n">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2819,19 +2819,19 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>18</v>
@@ -2840,7 +2840,7 @@
         <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>20</v>
@@ -2873,31 +2873,31 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="K51" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3035,31 +3035,31 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J56" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K56" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K56" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L56" s="12" t="n">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3305,47 +3305,47 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I57" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K57" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="M57" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J57" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>132</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3467,47 +3467,47 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>25</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>10</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>13</v>
@@ -3695,16 +3695,16 @@
         <v>3</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>20</v>
@@ -3737,19 +3737,19 @@
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>8</v>
@@ -3758,26 +3758,26 @@
         <v>3</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,39 +3787,39 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>3</v>
@@ -3857,19 +3857,19 @@
         <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3953,31 +3953,31 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4061,31 +4061,31 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L71" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M71" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L71" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4169,47 +4169,47 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="M73" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F73" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,39 +4327,39 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="H76" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="M76" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4385,31 +4385,31 @@
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,39 +4435,39 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4493,31 +4493,31 @@
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H79" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I79" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L79" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H81" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J81" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="I81" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="M82" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,39 +4705,39 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4763,19 +4763,19 @@
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J84" s="12" t="n">
         <v>6</v>
@@ -4784,26 +4784,26 @@
         <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,35 +4813,35 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H85" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L85" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="I85" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="M85" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,35 +4867,35 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
         <v>23</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4946,14 +4946,14 @@
         <v>2</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5000,10 +5000,10 @@
         <v>3</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>0</v>
@@ -5054,26 +5054,26 @@
         <v>0</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G90" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J90" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H90" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K90" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,51 +5137,51 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
         <v>14</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5230,12 +5230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5249,19 +5249,19 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J93" s="12" t="n">
         <v>3</v>
@@ -5270,26 +5270,26 @@
         <v>0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,32 +5299,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J94" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>0</v>
@@ -5338,12 +5338,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,35 +5353,35 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J95" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M95" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -5392,12 +5392,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5407,51 +5407,51 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N97" headerRowCount="1">
-  <autoFilter ref="A10:N97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N98" headerRowCount="1">
+  <autoFilter ref="A10:N98"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7886</v>
+        <v>8433</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6349</v>
+        <v>6795</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4958</v>
+        <v>5352</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>209</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>193</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>65</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="I19" s="12" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>215</v>
+        <v>297</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>154</v>
-      </c>
       <c r="G22" s="12" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>250</v>
+        <v>337</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H24" s="12" t="n">
+        <v>203</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="K24" s="12" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>335</v>
+        <v>400</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>324</v>
+        <v>163</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>55</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>12</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>40</v>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>74</v>
-      </c>
       <c r="J41" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,39 +2491,39 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2549,31 +2549,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2603,47 +2603,47 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>57</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>184</v>
+        <v>95</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>46</v>
+        <v>183</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>20</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="I51" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="H53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="J53" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>50</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,39 +3301,39 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3359,31 +3359,31 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3413,28 +3413,28 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>1</v>
@@ -3467,19 +3467,19 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>25</v>
@@ -3488,26 +3488,26 @@
         <v>12</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,20 +3517,20 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>38</v>
@@ -3539,13 +3539,13 @@
         <v>9</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,39 +3571,39 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3629,31 +3629,31 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G64" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,35 +3733,35 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J66" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="K66" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,39 +3841,39 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3899,28 +3899,28 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F68" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G68" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="J68" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>21</v>
@@ -3953,35 +3953,35 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4007,28 +4007,28 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>51</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>1</v>
@@ -4061,16 +4061,16 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>30</v>
@@ -4079,29 +4079,29 @@
         <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G72" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="H72" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="K72" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>21</v>
@@ -4187,10 +4187,10 @@
         <v>13</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>34</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K74" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M74" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F75" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I75" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G75" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J75" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
         <v>32</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J79" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,35 +4543,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
         <v>31</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4601,19 +4601,19 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>8</v>
@@ -4622,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>2</v>
@@ -4636,12 +4636,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L82" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M82" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4709,28 +4709,28 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>2</v>
@@ -4766,13 +4766,13 @@
         <v>26</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>24</v>
@@ -4784,14 +4784,14 @@
         <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4817,19 +4817,19 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>2</v>
@@ -4838,7 +4838,7 @@
         <v>12</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>3</v>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,35 +4867,35 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="M86" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,39 +4921,39 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4979,19 +4979,19 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J88" s="12" t="n">
         <v>5</v>
@@ -5000,10 +5000,10 @@
         <v>3</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -5014,12 +5014,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,51 +5029,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,51 +5083,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J90" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M90" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,35 +5137,35 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F91" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="H91" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5176,12 +5176,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,35 +5191,35 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5230,12 +5230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,51 +5245,51 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,17 +5299,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>0</v>
@@ -5318,32 +5318,32 @@
         <v>10</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
@@ -5363,29 +5363,29 @@
         <v>0</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>28</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5468,13 +5468,13 @@
         <v>6</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>23</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I97" s="12" t="n">
         <v>6</v>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>0</v>
@@ -5494,6 +5494,60 @@
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01409</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>NOVI LIGURE</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>DELUGAS NADIA</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N98" headerRowCount="1">
-  <autoFilter ref="A10:N98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N115" headerRowCount="1">
+  <autoFilter ref="A10:N115"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8433</v>
+        <v>10105</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6795</v>
+        <v>8035</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>5352</v>
+        <v>6368</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>02151</t>
+          <t>22960</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>AGRATE BRIANZA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -817,51 +817,51 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>386</v>
+        <v>579</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>38</v>
+        <v>869</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>261</v>
+        <v>434</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>775</v>
+        <v>726</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>02151</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SARONNO</t>
+          <t>AGRATE BRIANZA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>87</v>
+        <v>427</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>420</v>
+        <v>775</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LISSONE</t>
+          <t>SARONNO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>334</v>
+        <v>382</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>318</v>
+        <v>543</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>295</v>
+        <v>70</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>51998</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>LISSONE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>276</v>
+        <v>334</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>221</v>
+        <v>289</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>231</v>
+        <v>385</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>443</v>
+        <v>351</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>396</v>
+        <v>231</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02862</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASSANO MAGNAGO</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>278</v>
+        <v>396</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>02862</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>CASSANO MAGNAGO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02308</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>430</v>
+        <v>251</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02308</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>192</v>
+        <v>361</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>187</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>32</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>85</v>
+        <v>365</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>332</v>
+        <v>192</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>297</v>
+        <v>148</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>228</v>
+        <v>375</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>160</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>227</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>72</v>
-      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>400</v>
+        <v>297</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K25" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>66</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>295</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>16</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>351</v>
+        <v>227</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>263</v>
+        <v>337</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>232</v>
+        <v>400</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>140</v>
+        <v>236</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>255</v>
+        <v>118</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>338</v>
+        <v>212</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>219</v>
+        <v>338</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2111,53 +2111,49 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>GIURICIN ANTONIO</t>
-        </is>
-      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="12" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>134</v>
+        <v>396</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>77</v>
+        <v>606</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2163,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2202,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2217,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>158</v>
+        <v>269</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,46 +2271,46 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>85</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2329,35 +2325,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2364,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2379,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2433,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2472,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2487,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>243</v>
+        <v>158</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2541,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="H43" s="12" t="n">
+      <c r="J43" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L43" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>103</v>
-      </c>
       <c r="M43" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2595,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="F44" s="12" t="n">
+        <v>163</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>62</v>
-      </c>
       <c r="J44" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2649,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="J45" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="L45" s="12" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2703,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>54</v>
+        <v>239</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2742,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2757,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>188</v>
+        <v>243</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2811,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="H48" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J48" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="K48" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2865,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2904,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2919,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>195</v>
+        <v>87</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2973,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>57</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3027,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3081,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H53" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="J53" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3120,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3135,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K54" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L54" s="12" t="n">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3174,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3189,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="J55" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="K55" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3228,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3243,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3282,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3297,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3351,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,35 +3405,35 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3444,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3459,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3498,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3513,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3575,47 +3571,47 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3621,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3683,47 +3679,47 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,20 +3729,20 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="G65" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>49</v>
@@ -3755,29 +3751,29 @@
         <v>20</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>86</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3783,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>52</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3837,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3891,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3930,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3945,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J69" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +3999,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4053,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4107,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="G72" s="12" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4146,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4161,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,46 +4215,46 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4277,47 +4273,47 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4323,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M76" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4362,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4377,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J77" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,35 +4431,35 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4474,12 +4470,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4485,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J79" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K79" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L79" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4539,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4593,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,35 +4647,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4690,12 +4686,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4701,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,35 +4755,35 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J84" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -4798,12 +4794,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4817,31 +4813,31 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4848,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,51 +4863,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,35 +4917,35 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -4960,12 +4956,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,35 +4971,35 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -5014,12 +5010,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5029,51 +5025,51 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G89" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H89" s="12" t="n">
+      <c r="L89" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="M89" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L89" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M89" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,35 +5079,35 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
@@ -5122,12 +5118,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,11 +5133,11 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F91" s="12" t="n">
         <v>0</v>
@@ -5153,35 +5149,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5191,35 +5187,35 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -5230,12 +5226,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5245,35 +5241,35 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G93" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J93" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H93" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5284,12 +5280,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5299,35 +5295,35 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J94" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -5338,12 +5334,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5353,35 +5349,35 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F95" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K95" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K95" s="12" t="n">
+      <c r="L95" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="M95" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -5392,12 +5388,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5407,51 +5403,51 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5461,35 +5457,35 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -5500,52 +5496,962 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>52221</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>CERRI SARA</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>53490</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SANT'ILARIO D'ENZA</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>IACONA GIOVANNI</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>51919</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>PAULLO</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>CERRI SARA</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>00978</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>COLLEGNO</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>00728</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>POIRINO</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>PODESTÀ ANDREA</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>00585</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>PODESTÀ ANDREA</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>00015</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>COURMAYEUR</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>DELLI CARRI LUCA</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>52106</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>MILANO</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>ROMANO CARMELA</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>02925</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>CARDANO AL CAMPO</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>SALVINELLI LUCA</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L106" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>52952</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ALPIGNANO</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>51318</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA FEDERICO</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>22966</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>BERCETO</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>53507</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ALBA</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>GIARRATANA SEARA</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>01858</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>BREGNANO</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>00607</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>COLLEGNO</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>01923</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>CANTÙ</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>RAVA CLAUDIO</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>51654</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SANTHIÀ</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>BIANCHI ENRICO</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
           <t>01409</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>NOVI LIGURE</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E98" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I98" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M98" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N115" headerRowCount="1">
-  <autoFilter ref="A10:N115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N122" headerRowCount="1">
+  <autoFilter ref="A10:N122"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10105</v>
+        <v>10942</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8035</v>
+        <v>8669</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6368</v>
+        <v>6672</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02308</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>59</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>430</v>
+        <v>213</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>02308</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
         <v>248</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>226</v>
+        <v>361</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>365</v>
+        <v>430</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>187</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>86</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>148</v>
+        <v>365</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>375</v>
+        <v>196</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>332</v>
+        <v>264</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>255</v>
+        <v>332</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>160</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="L26" s="12" t="n">
-        <v>227</v>
+        <v>297</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>337</v>
+        <v>182</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>60</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>400</v>
+        <v>228</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>269</v>
+        <v>337</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>64</v>
+        <v>203</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>263</v>
+        <v>163</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>212</v>
+        <v>351</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,31 +1955,31 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>244</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>338</v>
+        <v>268</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2111,49 +2111,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>BIANCHI ENRICO</t>
+        </is>
+      </c>
       <c r="E35" s="12" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>396</v>
+        <v>136</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>606</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>53</v>
+        <v>255</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2215,53 +2219,49 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>GUERRA GIUSEPPE</t>
-        </is>
-      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>149</v>
+        <v>396</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>606</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L37" s="12" t="n">
-        <v>269</v>
+        <v>161</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2271,51 +2271,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>295</v>
+        <v>112</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,51 +2325,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,35 +2379,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>117</v>
+        <v>295</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,35 +2433,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2472,12 +2472,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2487,51 +2487,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,51 +2541,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,35 +2649,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>83</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2688,12 +2688,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,35 +2703,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>163</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="H46" s="12" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2742,12 +2742,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2757,51 +2757,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2811,35 +2811,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="H48" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>83</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>64</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2850,12 +2850,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2865,51 +2865,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2919,51 +2919,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2973,51 +2973,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3027,51 +3027,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3081,51 +3081,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>188</v>
+        <v>87</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3135,35 +3135,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K54" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3174,12 +3174,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3189,51 +3189,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3243,51 +3243,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>57</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K56" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="M56" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L56" s="12" t="n">
-        <v>195</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3297,51 +3297,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3351,51 +3351,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3405,51 +3405,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G59" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I59" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H59" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="J59" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3459,51 +3459,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>87</v>
+        <v>167</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,47 +3517,47 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="J61" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K61" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>67</v>
-      </c>
       <c r="M61" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3567,51 +3567,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3621,35 +3621,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3660,12 +3660,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3675,51 +3675,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>76</v>
+        <v>184</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3729,51 +3729,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3783,51 +3783,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3837,35 +3837,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3876,12 +3876,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3891,35 +3891,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="M68" s="12" t="n">
         <v>24</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>76</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3930,12 +3930,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3945,35 +3945,35 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3984,12 +3984,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3999,35 +3999,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4038,12 +4038,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4053,35 +4053,35 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F71" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="H71" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4092,12 +4092,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4107,35 +4107,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G72" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4146,12 +4146,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4161,51 +4161,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4215,51 +4215,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="K74" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4269,51 +4269,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4323,51 +4323,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="I76" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="J76" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4377,35 +4377,35 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4416,12 +4416,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4431,51 +4431,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4485,35 +4485,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4524,12 +4524,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4539,35 +4539,35 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I80" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I80" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J80" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -4578,12 +4578,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4593,51 +4593,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4647,35 +4647,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I82" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="J82" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4686,12 +4686,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4701,51 +4701,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4755,51 +4755,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4809,51 +4809,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4863,51 +4863,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4917,35 +4917,35 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -4956,12 +4956,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4971,51 +4971,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H88" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M88" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5025,35 +5025,35 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5064,12 +5064,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5079,51 +5079,51 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5137,31 +5137,31 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J91" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K91" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L91" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M91" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="M91" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -5172,12 +5172,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5187,51 +5187,51 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I92" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F92" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="J92" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="M92" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K92" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L92" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5241,35 +5241,35 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F93" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J93" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5280,12 +5280,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5295,51 +5295,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F94" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H94" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G94" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="I94" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5349,51 +5349,51 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J95" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5403,51 +5403,51 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J96" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K96" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L96" s="12" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5457,51 +5457,51 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5511,51 +5511,51 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J98" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5565,51 +5565,51 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M99" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H99" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5623,47 +5623,47 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5673,51 +5673,51 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I101" s="12" t="n">
         <v>20</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="J101" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M101" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5727,51 +5727,51 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M102" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5781,51 +5781,51 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5835,51 +5835,51 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="M104" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5889,51 +5889,51 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>5</v>
+        <v>193</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="M105" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5943,51 +5943,51 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G106" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K106" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="n">
+      <c r="L106" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M106" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J106" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5997,51 +5997,51 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J107" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K107" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6051,51 +6051,51 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F108" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G108" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J108" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6105,51 +6105,51 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J109" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L109" s="12" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6159,51 +6159,51 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J110" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M110" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>01858</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>BREGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6211,49 +6211,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>PODESTÀ ANDREA</t>
+        </is>
+      </c>
       <c r="E111" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>00607</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6261,49 +6265,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>DELLI CARRI LUCA</t>
+        </is>
+      </c>
       <c r="E112" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K112" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>01923</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CANTÙ</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6313,51 +6321,51 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J113" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M113" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K113" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6367,26 +6375,26 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F114" s="12" t="n">
         <v>42</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I114" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J114" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K114" s="12" t="n">
         <v>0</v>
@@ -6395,23 +6403,23 @@
         <v>36</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6421,39 +6429,413 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>52952</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ALPIGNANO</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>GUERRA GIUSEPPE</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J116" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>22966</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>BERCETO</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>53507</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ALBA</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>GIARRATANA SEARA</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>01858</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>BREGNANO</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L119" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>51654</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SANTHIÀ</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>BIANCHI ENRICO</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>01409</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>NOVI LIGURE</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>DELUGAS NADIA</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
           <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>01416</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SERRAVALLE SCRIVIA</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>DELUGAS NADIA</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N122" headerRowCount="1">
-  <autoFilter ref="A10:N122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N121" headerRowCount="1">
+  <autoFilter ref="A10:N121"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10942</v>
+        <v>10934</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8669</v>
+        <v>8659</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6672</v>
+        <v>6671</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -6630,12 +6630,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01858</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>BREGNANO</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6643,30 +6643,34 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>BIANCHI ENRICO</t>
+        </is>
+      </c>
       <c r="E119" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>0</v>
@@ -6680,12 +6684,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6695,51 +6699,51 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6753,19 +6757,19 @@
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I121" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="J121" s="12" t="n">
         <v>0</v>
@@ -6774,66 +6778,12 @@
         <v>0</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N121" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>01416</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>SERRAVALLE SCRIVIA</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>DELUGAS NADIA</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="I122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -676,13 +676,13 @@
         <v>111</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10934</v>
+        <v>11082</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8659</v>
+        <v>8779</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6671</v>
+        <v>6759</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00120</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COSSATO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>136</v>
+        <v>231</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>00120</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>COSSATO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>255</v>
+        <v>43</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2219,49 +2219,53 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>DELLERBA ALBERTO</t>
+        </is>
+      </c>
       <c r="E37" s="12" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>396</v>
+        <v>140</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>606</v>
+        <v>52</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>161</v>
+        <v>338</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2269,37 +2273,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>CARCIONE PARIDE</t>
-        </is>
-      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>174</v>
+        <v>396</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>95</v>
+        <v>606</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2310,12 +2310,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,51 +2325,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>269</v>
+        <v>112</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2379,35 +2379,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2433,51 +2433,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2487,51 +2487,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>117</v>
+        <v>219</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2541,51 +2541,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2649,35 +2649,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2688,12 +2688,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2703,51 +2703,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2757,51 +2757,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K47" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L47" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2811,51 +2811,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I48" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L48" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J48" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K48" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>239</v>
-      </c>
       <c r="M48" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2865,35 +2865,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2919,35 +2919,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2958,12 +2958,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2973,35 +2973,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3012,12 +3012,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3027,51 +3027,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F52" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="H52" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>44</v>
-      </c>
       <c r="I52" s="12" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3081,35 +3081,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3135,51 +3135,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3189,51 +3189,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3243,51 +3243,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L56" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>188</v>
-      </c>
       <c r="M56" s="12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3297,35 +3297,35 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
@@ -3336,12 +3336,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3351,51 +3351,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3405,51 +3405,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3459,35 +3459,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>73</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>57</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3498,12 +3498,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3513,51 +3513,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3567,51 +3567,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3621,51 +3621,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3675,35 +3675,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
         <v>67</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>56</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3714,12 +3714,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3729,51 +3729,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
         <v>67</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3783,51 +3783,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J66" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K66" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K66" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="L66" s="12" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3837,51 +3837,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3891,35 +3891,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
         <v>63</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3930,12 +3930,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3945,51 +3945,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
         <v>63</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H69" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I69" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3999,51 +3999,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
         <v>63</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4053,51 +4053,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4107,35 +4107,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
         <v>60</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4146,12 +4146,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4161,51 +4161,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
         <v>60</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4215,51 +4215,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
         <v>60</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4269,51 +4269,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4323,51 +4323,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4377,51 +4377,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="G77" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K77" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>164</v>
+      </c>
+      <c r="M77" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H77" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L77" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4431,35 +4431,35 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K78" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="M78" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4470,12 +4470,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4485,51 +4485,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
         <v>50</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4539,51 +4539,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4593,51 +4593,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4647,35 +4647,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4686,12 +4686,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4701,35 +4701,35 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4740,12 +4740,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4755,51 +4755,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
         <v>45</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4809,51 +4809,51 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L85" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J85" s="12" t="n">
+      <c r="M85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K85" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M85" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4863,51 +4863,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
         <v>43</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4917,35 +4917,35 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
         <v>43</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -4956,12 +4956,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4971,51 +4971,51 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5025,35 +5025,35 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -5064,12 +5064,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5083,47 +5083,47 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G90" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F90" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="H90" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5133,51 +5133,51 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
         <v>37</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G91" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H91" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I91" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5187,51 +5187,51 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
         <v>37</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5241,51 +5241,51 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5295,51 +5295,51 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5349,35 +5349,35 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H95" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J95" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I95" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K95" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -5388,12 +5388,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5403,51 +5403,51 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J96" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
@@ -5467,29 +5467,29 @@
         <v>0</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K97" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="M97" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L97" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N121" headerRowCount="1">
-  <autoFilter ref="A10:N121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N124" headerRowCount="1">
+  <autoFilter ref="A10:N124"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>11082</v>
@@ -6789,6 +6789,168 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>02667</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>PIACENZA</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>GIURICIN ANTONIO</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>16435</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>CORREGGIO</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>22973</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>FIDENZA</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>IACOPINI ALESSANDRA</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N124" headerRowCount="1">
-  <autoFilter ref="A10:N124"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O124" headerRowCount="1">
+  <autoFilter ref="A10:O124"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE EUROPA 111A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>579</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>479</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>474</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>869</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>726</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MATTEOTTI 133</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>386</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>427</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>775</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROMA ANGOLO VIA IMOLA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>382</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>543</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>420</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>V. MATTEOTTI ANG. COMO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>334</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>385</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STRADA PROV.LE N.23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>443</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>396</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MARIO ALBINO BONICALZA 127</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>437</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>278</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>251</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO ALESSANDRIA 494</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>245</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>213</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE L. CADORNA 60</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>361</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>430</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GRAMSCI, 9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA TORINO 135</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>222</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA FARNESIANA 151</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>375</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS20 KM12+230</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS33KM24+86 - SEMPIONE</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>297</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MILANO 10</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA EMILIA, 70</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>337</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>232</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA RISORGIMENTO 12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROSSELLI 19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GIUSEPPE  MAZZINI SNC</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>148</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VAI CAMILLO CAMPARI</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2270,38 +2421,43 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="12" t="n">
+          <t>VIA NOVARA</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>396</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>606</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2320,42 +2476,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MARTIRI DI CERVAROLO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2374,42 +2535,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2428,42 +2594,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>85</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>35</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L41" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2482,42 +2653,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2536,42 +2712,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2590,42 +2771,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>77</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>39</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L44" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M44" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2644,42 +2830,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2698,42 +2889,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="N46" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2752,42 +2948,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2806,42 +3007,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M48" s="12" t="n">
+      <c r="N48" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2860,42 +3066,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="M49" s="12" t="n">
+      <c r="N49" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2914,42 +3125,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA LIGURIA 1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="L50" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L50" s="12" t="n">
+      <c r="M50" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M50" s="12" t="n">
+      <c r="N50" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2968,42 +3184,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="I51" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="J51" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="L51" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3022,42 +3243,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="K52" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K52" s="12" t="n">
+      <c r="L52" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="M52" s="12" t="n">
+      <c r="N52" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3076,42 +3302,47 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="I53" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="J53" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="K53" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="K53" s="12" t="n">
+      <c r="L53" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L53" s="12" t="n">
+      <c r="M53" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M53" s="12" t="n">
+      <c r="N53" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3130,42 +3361,47 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 11 KM 25+300</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="J54" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="K54" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K54" s="12" t="n">
+      <c r="L54" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L54" s="12" t="n">
+      <c r="M54" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M54" s="12" t="n">
+      <c r="N54" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3184,42 +3420,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H55" s="12" t="n">
+      <c r="I55" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="J55" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K55" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K55" s="12" t="n">
+      <c r="L55" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L55" s="12" t="n">
+      <c r="M55" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="M55" s="12" t="n">
+      <c r="N55" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3238,42 +3479,47 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="F56" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="G56" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G56" s="12" t="n">
+      <c r="H56" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="I56" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="J56" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="K56" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="L56" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="M56" s="12" t="n">
+      <c r="N56" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3292,42 +3538,47 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="F57" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="G57" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="G57" s="12" t="n">
+      <c r="H57" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="H57" s="12" t="n">
+      <c r="I57" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="J57" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="K57" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K57" s="12" t="n">
+      <c r="L57" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L57" s="12" t="n">
+      <c r="M57" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="M57" s="12" t="n">
+      <c r="N57" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3346,42 +3597,47 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="F58" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="G58" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="H58" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="I58" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="K58" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K58" s="12" t="n">
+      <c r="L58" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L58" s="12" t="n">
+      <c r="M58" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M58" s="12" t="n">
+      <c r="N58" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3400,42 +3656,47 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="F59" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="G59" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="G59" s="12" t="n">
+      <c r="H59" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="H59" s="12" t="n">
+      <c r="I59" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="J59" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="K59" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K59" s="12" t="n">
+      <c r="L59" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L59" s="12" t="n">
+      <c r="M59" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M59" s="12" t="n">
+      <c r="N59" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3454,42 +3715,47 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="F60" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F60" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="G60" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="J60" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="K60" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K60" s="12" t="n">
+      <c r="L60" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L60" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="M60" s="12" t="n">
+      <c r="N60" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3508,42 +3774,47 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="F61" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="G61" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="I61" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="K61" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L61" s="12" t="n">
+      <c r="M61" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M61" s="12" t="n">
+      <c r="N61" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3562,42 +3833,47 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="F62" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F62" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="H62" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="K62" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="M62" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="N62" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3616,42 +3892,47 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="J63" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="K63" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K63" s="12" t="n">
+      <c r="L63" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L63" s="12" t="n">
+      <c r="M63" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="M63" s="12" t="n">
+      <c r="N63" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3670,42 +3951,47 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="F64" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F64" s="12" t="n">
+      <c r="G64" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G64" s="12" t="n">
+      <c r="H64" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="I64" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="J64" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="K64" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K64" s="12" t="n">
+      <c r="L64" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L64" s="12" t="n">
+      <c r="M64" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="M64" s="12" t="n">
+      <c r="N64" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3724,42 +4010,47 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G65" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="H65" s="12" t="n">
+      <c r="I65" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I65" s="12" t="n">
+      <c r="J65" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="K65" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K65" s="12" t="n">
+      <c r="L65" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L65" s="12" t="n">
+      <c r="M65" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M65" s="12" t="n">
+      <c r="N65" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3778,42 +4069,47 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="F66" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F66" s="12" t="n">
+      <c r="G66" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G66" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="I66" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="J66" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="K66" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K66" s="12" t="n">
+      <c r="L66" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L66" s="12" t="n">
+      <c r="M66" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M66" s="12" t="n">
+      <c r="N66" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3832,42 +4128,47 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="L67" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L67" s="12" t="n">
+      <c r="M67" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="M67" s="12" t="n">
+      <c r="N67" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3886,42 +4187,47 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STR. STATALE 31 KM 22+335</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="F68" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F68" s="12" t="n">
+      <c r="G68" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="G68" s="12" t="n">
+      <c r="H68" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H68" s="12" t="n">
+      <c r="I68" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="J68" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="K68" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K68" s="12" t="n">
+      <c r="L68" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L68" s="12" t="n">
+      <c r="M68" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M68" s="12" t="n">
+      <c r="N68" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3940,42 +4246,47 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="J69" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="K69" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K69" s="12" t="n">
+      <c r="L69" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L69" s="12" t="n">
+      <c r="M69" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="M69" s="12" t="n">
+      <c r="N69" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3994,42 +4305,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F70" s="12" t="n">
+      <c r="G70" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="G70" s="12" t="n">
+      <c r="H70" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="I70" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I70" s="12" t="n">
+      <c r="J70" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="K70" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K70" s="12" t="n">
+      <c r="L70" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L70" s="12" t="n">
+      <c r="M70" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M70" s="12" t="n">
+      <c r="N70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4048,42 +4364,47 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CISA LIGURE 10</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F71" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G71" s="12" t="n">
+      <c r="H71" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H71" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="J71" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="K71" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L71" s="12" t="n">
+      <c r="M71" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M71" s="12" t="n">
+      <c r="N71" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4102,42 +4423,47 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="F72" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>58</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M72" s="12" t="n">
+      <c r="N72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4156,42 +4482,47 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="F73" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F73" s="12" t="n">
+      <c r="G73" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G73" s="12" t="n">
+      <c r="H73" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H73" s="12" t="n">
+      <c r="I73" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I73" s="12" t="n">
+      <c r="J73" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="K73" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K73" s="12" t="n">
+      <c r="L73" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L73" s="12" t="n">
+      <c r="M73" s="12" t="n">
         <v>195</v>
       </c>
-      <c r="M73" s="12" t="n">
+      <c r="N73" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4210,42 +4541,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S. 10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="F74" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F74" s="12" t="n">
+      <c r="G74" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G74" s="12" t="n">
+      <c r="H74" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="H74" s="12" t="n">
+      <c r="I74" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="J74" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L74" s="12" t="n">
+      <c r="M74" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M74" s="12" t="n">
+      <c r="N74" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4264,42 +4600,47 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="F75" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F75" s="12" t="n">
+      <c r="G75" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G75" s="12" t="n">
+      <c r="H75" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="I75" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I75" s="12" t="n">
+      <c r="J75" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="K75" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K75" s="12" t="n">
+      <c r="L75" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L75" s="12" t="n">
+      <c r="M75" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M75" s="12" t="n">
+      <c r="N75" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4318,42 +4659,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="F76" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F76" s="12" t="n">
+      <c r="G76" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G76" s="12" t="n">
+      <c r="H76" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H76" s="12" t="n">
+      <c r="I76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="12" t="n">
+      <c r="J76" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="K76" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K76" s="12" t="n">
+      <c r="L76" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L76" s="12" t="n">
+      <c r="M76" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="M76" s="12" t="n">
+      <c r="N76" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4372,42 +4718,47 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="F77" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="G77" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="H77" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="I77" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="J77" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="K77" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="L77" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="M77" s="12" t="n">
         <v>164</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="N77" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4426,42 +4777,47 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="F78" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F78" s="12" t="n">
+      <c r="G78" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G78" s="12" t="n">
+      <c r="H78" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="I78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="J78" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J78" s="12" t="n">
+      <c r="K78" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K78" s="12" t="n">
+      <c r="L78" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L78" s="12" t="n">
+      <c r="M78" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="M78" s="12" t="n">
+      <c r="N78" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4480,42 +4836,47 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="F79" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F79" s="12" t="n">
+      <c r="G79" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G79" s="12" t="n">
+      <c r="H79" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H79" s="12" t="n">
+      <c r="I79" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="J79" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J79" s="12" t="n">
+      <c r="K79" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K79" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M79" s="12" t="n">
+      <c r="N79" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4534,42 +4895,47 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>TANG.TO SUD-RACC. DROSSO</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>RAMPONE ROBERTO</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="F80" s="12" t="n">
         <v>50</v>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>52</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>52</v>
       </c>
       <c r="H80" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="I80" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="J80" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="K80" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="L80" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="M80" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="N80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4588,42 +4954,47 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F81" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G81" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I81" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J81" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K81" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L81" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="M81" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4642,42 +5013,47 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="F82" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F82" s="12" t="n">
+      <c r="G82" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G82" s="12" t="n">
+      <c r="H82" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="H82" s="12" t="n">
+      <c r="I82" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="I82" s="12" t="n">
+      <c r="J82" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K82" s="12" t="n">
+      <c r="L82" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L82" s="12" t="n">
+      <c r="M82" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M82" s="12" t="n">
+      <c r="N82" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4696,42 +5072,47 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="F83" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="K83" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M83" s="12" t="n">
+      <c r="N83" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4750,42 +5131,47 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="F84" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F84" s="12" t="n">
+      <c r="G84" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G84" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J84" s="12" t="n">
+      <c r="K84" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K84" s="12" t="n">
+      <c r="L84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L84" s="12" t="n">
+      <c r="M84" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M84" s="12" t="n">
+      <c r="N84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4804,42 +5190,47 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="F85" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F85" s="12" t="n">
+      <c r="G85" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G85" s="12" t="n">
+      <c r="H85" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H85" s="12" t="n">
+      <c r="I85" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I85" s="12" t="n">
+      <c r="J85" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J85" s="12" t="n">
+      <c r="K85" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K85" s="12" t="n">
+      <c r="L85" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L85" s="12" t="n">
+      <c r="M85" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M85" s="12" t="n">
+      <c r="N85" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4858,42 +5249,47 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>CARCIONE PARIDE</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="F86" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="K86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K86" s="12" t="n">
+      <c r="L86" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L86" s="12" t="n">
+      <c r="M86" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="N86" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4912,42 +5308,47 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
+      <c r="F87" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F87" s="12" t="n">
+      <c r="G87" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G87" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H87" s="12" t="n">
+      <c r="I87" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I87" s="12" t="n">
+      <c r="J87" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J87" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K87" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L87" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M87" s="12" t="n">
+      <c r="N87" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4966,42 +5367,47 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
+      <c r="F88" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F88" s="12" t="n">
+      <c r="G88" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G88" s="12" t="n">
+      <c r="H88" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H88" s="12" t="n">
+      <c r="I88" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="I88" s="12" t="n">
+      <c r="J88" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J88" s="12" t="n">
+      <c r="K88" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K88" s="12" t="n">
+      <c r="L88" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L88" s="12" t="n">
+      <c r="M88" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M88" s="12" t="n">
+      <c r="N88" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5020,42 +5426,47 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n">
+      <c r="F89" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F89" s="12" t="n">
+      <c r="G89" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G89" s="12" t="n">
+      <c r="H89" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H89" s="12" t="n">
+      <c r="I89" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="12" t="n">
+      <c r="J89" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J89" s="12" t="n">
+      <c r="K89" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="12" t="n">
+      <c r="L89" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L89" s="12" t="n">
+      <c r="M89" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M89" s="12" t="n">
+      <c r="N89" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5074,42 +5485,47 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n">
+      <c r="F90" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F90" s="12" t="n">
+      <c r="G90" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G90" s="12" t="n">
+      <c r="H90" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H90" s="12" t="n">
+      <c r="I90" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I90" s="12" t="n">
+      <c r="J90" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="K90" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K90" s="12" t="n">
+      <c r="L90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L90" s="12" t="n">
+      <c r="M90" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M90" s="12" t="n">
+      <c r="N90" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5128,42 +5544,47 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E91" s="12" t="n">
+      <c r="F91" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F91" s="12" t="n">
+      <c r="G91" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G91" s="12" t="n">
+      <c r="H91" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H91" s="12" t="n">
+      <c r="I91" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I91" s="12" t="n">
+      <c r="J91" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J91" s="12" t="n">
+      <c r="K91" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K91" s="12" t="n">
+      <c r="L91" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L91" s="12" t="n">
+      <c r="M91" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M91" s="12" t="n">
+      <c r="N91" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5182,42 +5603,47 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n">
+      <c r="F92" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J92" s="12" t="n">
+      <c r="K92" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K92" s="12" t="n">
+      <c r="L92" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L92" s="12" t="n">
+      <c r="M92" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M92" s="12" t="n">
+      <c r="N92" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5236,42 +5662,47 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E93" s="12" t="n">
+      <c r="F93" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F93" s="12" t="n">
+      <c r="G93" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G93" s="12" t="n">
+      <c r="H93" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H93" s="12" t="n">
+      <c r="I93" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I93" s="12" t="n">
+      <c r="J93" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J93" s="12" t="n">
+      <c r="K93" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K93" s="12" t="n">
+      <c r="L93" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L93" s="12" t="n">
+      <c r="M93" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="M93" s="12" t="n">
+      <c r="N93" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5290,42 +5721,47 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="F94" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F94" s="12" t="n">
+      <c r="G94" s="12" t="n">
         <v>55</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I94" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="K94" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K94" s="12" t="n">
+      <c r="L94" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L94" s="12" t="n">
+      <c r="M94" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M94" s="12" t="n">
+      <c r="N94" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5344,42 +5780,47 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E95" s="12" t="n">
+      <c r="F95" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F95" s="12" t="n">
+      <c r="G95" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G95" s="12" t="n">
+      <c r="H95" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H95" s="12" t="n">
+      <c r="I95" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I95" s="12" t="n">
+      <c r="J95" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J95" s="12" t="n">
+      <c r="K95" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K95" s="12" t="n">
+      <c r="L95" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L95" s="12" t="n">
+      <c r="M95" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="M95" s="12" t="n">
+      <c r="N95" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5398,42 +5839,47 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E96" s="12" t="n">
+      <c r="F96" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F96" s="12" t="n">
+      <c r="G96" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G96" s="12" t="n">
+      <c r="H96" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H96" s="12" t="n">
+      <c r="I96" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I96" s="12" t="n">
+      <c r="J96" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J96" s="12" t="n">
+      <c r="K96" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K96" s="12" t="n">
+      <c r="L96" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L96" s="12" t="n">
+      <c r="M96" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="M96" s="12" t="n">
+      <c r="N96" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5452,42 +5898,47 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E97" s="12" t="n">
+      <c r="F97" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F97" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="H97" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J97" s="12" t="n">
+      <c r="K97" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K97" s="12" t="n">
+      <c r="L97" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L97" s="12" t="n">
+      <c r="M97" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M97" s="12" t="n">
+      <c r="N97" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5506,42 +5957,47 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E98" s="12" t="n">
+      <c r="F98" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F98" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H98" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="K98" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K98" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="M98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="N98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5560,42 +6016,47 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="F99" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="G99" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="H99" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="I99" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="J99" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="K99" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="L99" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="M99" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="N99" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5614,42 +6075,47 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="F100" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F100" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G100" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H100" s="12" t="n">
+      <c r="I100" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I100" s="12" t="n">
+      <c r="J100" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J100" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K100" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L100" s="12" t="n">
+      <c r="M100" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M100" s="12" t="n">
+      <c r="N100" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5668,42 +6134,47 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E101" s="12" t="n">
+      <c r="F101" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F101" s="12" t="n">
+      <c r="G101" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G101" s="12" t="n">
+      <c r="H101" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H101" s="12" t="n">
+      <c r="I101" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I101" s="12" t="n">
+      <c r="J101" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J101" s="12" t="n">
+      <c r="K101" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K101" s="12" t="n">
+      <c r="L101" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L101" s="12" t="n">
+      <c r="M101" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M101" s="12" t="n">
+      <c r="N101" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N101" s="2" t="inlineStr">
+      <c r="O101" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5722,42 +6193,47 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
           <t>VIGNADUZZO EDI</t>
         </is>
       </c>
-      <c r="E102" s="12" t="n">
+      <c r="F102" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F102" s="12" t="n">
+      <c r="G102" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G102" s="12" t="n">
+      <c r="H102" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="I102" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I102" s="12" t="n">
+      <c r="J102" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="K102" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K102" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M102" s="12" t="n">
+      <c r="N102" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5776,42 +6252,47 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
           <t>SVANINI EDOARDO</t>
         </is>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="F103" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F103" s="12" t="n">
+      <c r="G103" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="H103" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I103" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J103" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J103" s="12" t="n">
+      <c r="K103" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K103" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M103" s="12" t="n">
+      <c r="N103" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5830,42 +6311,47 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="F104" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F104" s="12" t="n">
+      <c r="G104" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G104" s="12" t="n">
+      <c r="H104" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="I104" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="J104" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="K104" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="L104" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L104" s="12" t="n">
+      <c r="M104" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M104" s="12" t="n">
+      <c r="N104" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5884,42 +6370,47 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="F105" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F105" s="12" t="n">
+      <c r="G105" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G105" s="12" t="n">
+      <c r="H105" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="I105" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="I105" s="12" t="n">
+      <c r="J105" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J105" s="12" t="n">
+      <c r="K105" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K105" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M105" s="12" t="n">
+      <c r="N105" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5938,42 +6429,47 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E106" s="12" t="n">
+      <c r="F106" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F106" s="12" t="n">
+      <c r="G106" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G106" s="12" t="n">
+      <c r="H106" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="I106" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="J106" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J106" s="12" t="n">
+      <c r="K106" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K106" s="12" t="n">
+      <c r="L106" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L106" s="12" t="n">
+      <c r="M106" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M106" s="12" t="n">
+      <c r="N106" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -5992,42 +6488,47 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>IACONA GIOVANNI</t>
         </is>
       </c>
-      <c r="E107" s="12" t="n">
+      <c r="F107" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F107" s="12" t="n">
+      <c r="G107" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G107" s="12" t="n">
+      <c r="H107" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H107" s="12" t="n">
+      <c r="I107" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I107" s="12" t="n">
+      <c r="J107" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K107" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L107" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M107" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M107" s="12" t="n">
+      <c r="N107" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -6046,42 +6547,47 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="F108" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F108" s="12" t="n">
+      <c r="G108" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="H108" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="I108" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="J108" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="K108" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K108" s="12" t="n">
+      <c r="L108" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L108" s="12" t="n">
+      <c r="M108" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="M108" s="12" t="n">
+      <c r="N108" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -6100,42 +6606,47 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="F109" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F109" s="12" t="n">
+      <c r="G109" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="H109" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H109" s="12" t="n">
+      <c r="I109" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="J109" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J109" s="12" t="n">
+      <c r="K109" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K109" s="12" t="n">
+      <c r="L109" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L109" s="12" t="n">
+      <c r="M109" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M109" s="12" t="n">
+      <c r="N109" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -6154,42 +6665,47 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="F110" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F110" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H110" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J110" s="12" t="n">
+      <c r="K110" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K110" s="12" t="n">
+      <c r="L110" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="M110" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="N110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -6208,42 +6724,47 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E111" s="12" t="n">
+      <c r="F111" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F111" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H111" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J111" s="12" t="n">
+      <c r="K111" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K111" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M111" s="12" t="n">
+      <c r="N111" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -6262,42 +6783,47 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="F112" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F112" s="12" t="n">
+      <c r="G112" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G112" s="12" t="n">
+      <c r="H112" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H112" s="12" t="n">
+      <c r="I112" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="J112" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J112" s="12" t="n">
+      <c r="K112" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K112" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L112" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="N112" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6316,42 +6842,47 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E113" s="12" t="n">
+      <c r="F113" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F113" s="12" t="n">
+      <c r="G113" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G113" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="J113" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="K113" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="L113" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="M113" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="N113" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6370,42 +6901,47 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>GALVANI 34</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="F114" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F114" s="12" t="n">
+      <c r="G114" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="I114" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I114" s="12" t="n">
+      <c r="J114" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J114" s="12" t="n">
+      <c r="K114" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K114" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M114" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6424,42 +6960,47 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S.336 PER MALPENSA  KM.8+500</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
           <t>SALVINELLI LUCA</t>
         </is>
       </c>
-      <c r="E115" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F115" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H115" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="M115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" s="2" t="inlineStr">
+      <c r="N115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6478,42 +7019,47 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E116" s="12" t="n">
+      <c r="F116" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F116" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H116" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J116" s="12" t="n">
+      <c r="K116" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K116" s="12" t="n">
+      <c r="L116" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L116" s="12" t="n">
+      <c r="M116" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="N116" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6532,42 +7078,47 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
           <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
-      <c r="E117" s="12" t="n">
+      <c r="F117" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F117" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H117" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="K117" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K117" s="12" t="n">
+      <c r="L117" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L117" s="12" t="n">
+      <c r="M117" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6586,42 +7137,47 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="F118" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F118" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H118" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J118" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="M118" s="12" t="n">
+      <c r="N118" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6640,42 +7196,47 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>DUE GIUGNO</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
           <t>BIANCHI ENRICO</t>
         </is>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="F119" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F119" s="12" t="n">
+      <c r="G119" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="H119" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H119" s="12" t="n">
+      <c r="I119" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="J119" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J119" s="12" t="n">
+      <c r="K119" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K119" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="2" t="inlineStr">
+      <c r="N119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -6694,20 +7255,22 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E120" s="12" t="n">
+      <c r="F120" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G120" s="12" t="n">
         <v>0</v>
       </c>
@@ -6715,11 +7278,11 @@
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" s="12" t="n">
         <v>0</v>
       </c>
@@ -6729,7 +7292,10 @@
       <c r="M120" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="N120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -6748,29 +7314,31 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
           <t>DELUGAS NADIA</t>
         </is>
       </c>
-      <c r="E121" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G121" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="I121" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J121" s="12" t="n">
         <v>0</v>
       </c>
@@ -6778,12 +7346,15 @@
         <v>0</v>
       </c>
       <c r="L121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" s="2" t="inlineStr">
+      <c r="N121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -6802,17 +7373,19 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MANFREDI 74</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
           <t>GIURICIN ANTONIO</t>
         </is>
       </c>
-      <c r="E122" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F122" s="12" t="n">
         <v>0</v>
       </c>
@@ -6837,7 +7410,10 @@
       <c r="M122" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="N122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6856,17 +7432,19 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA SS468</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
           <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
-      <c r="E123" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F123" s="12" t="n">
         <v>0</v>
       </c>
@@ -6891,7 +7469,10 @@
       <c r="M123" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N123" s="2" t="inlineStr">
+      <c r="N123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -6910,17 +7491,19 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t xml:space="preserve">LOC SAN MICHELE </t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
           <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
-      <c r="E124" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F124" s="12" t="n">
         <v>0</v>
       </c>
@@ -6945,7 +7528,10 @@
       <c r="M124" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N124" s="2" t="inlineStr">
+      <c r="N124" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O124" headerRowCount="1">
-  <autoFilter ref="A10:O124"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O123" headerRowCount="1">
+  <autoFilter ref="A10:O123"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>11082</v>
+        <v>11051</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8779</v>
+        <v>8757</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6759</v>
+        <v>6733</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -6065,17 +6065,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6085,35 +6085,35 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H100" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K100" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N100" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -6124,17 +6124,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6144,56 +6144,56 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H101" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I101" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="N101" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6203,56 +6203,56 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
         <v>26</v>
       </c>
       <c r="G102" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H102" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="N102" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6262,56 +6262,56 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
         <v>26</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="H103" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J103" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I103" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="K103" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="N103" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,35 +6321,35 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="J104" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G104" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="K104" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N104" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="N104" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6360,17 +6360,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6380,35 +6380,35 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6419,17 +6419,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6439,35 +6439,35 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6478,17 +6478,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6498,35 +6498,35 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H107" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I107" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I107" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="J107" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6537,17 +6537,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6557,20 +6557,20 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="12" t="n">
         <v>19</v>
@@ -6582,31 +6582,31 @@
         <v>3</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6616,35 +6616,35 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L109" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H109" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="M109" s="12" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="N109" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6655,17 +6655,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6679,31 +6679,31 @@
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="N110" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6714,17 +6714,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6734,56 +6734,56 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H111" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K111" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="N111" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6793,35 +6793,35 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K112" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="N112" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6832,17 +6832,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>GALVANI 34</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6852,35 +6852,35 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I113" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K113" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="N113" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6891,17 +6891,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GALVANI 34</t>
+          <t>S.S.336 PER MALPENSA  KM.8+500</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6911,35 +6911,35 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K114" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J114" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K114" s="12" t="n">
+      <c r="L114" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L114" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M114" s="12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6950,17 +6950,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>S.S.336 PER MALPENSA  KM.8+500</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6970,17 +6970,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I115" s="12" t="n">
         <v>0</v>
@@ -6989,13 +6989,13 @@
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="M115" s="12" t="n">
-        <v>28</v>
       </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
@@ -7009,17 +7009,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7029,23 +7029,23 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K116" s="12" t="n">
         <v>3</v>
@@ -7054,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N116" s="12" t="n">
         <v>0</v>
@@ -7068,17 +7068,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I117" s="12" t="n">
         <v>0</v>
@@ -7107,16 +7107,16 @@
         <v>9</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -7127,17 +7127,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>DUE GIUGNO</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7147,56 +7147,56 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N118" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>DUE GIUGNO</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7206,56 +7206,56 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7269,52 +7269,52 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>02667</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA MANFREDI 74</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7324,20 +7324,20 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J121" s="12" t="n">
         <v>0</v>
@@ -7349,31 +7349,31 @@
         <v>0</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>02667</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>VIA MANFREDI 74</t>
+          <t>VIA SS468</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
@@ -7422,17 +7422,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>VIA SS468</t>
+          <t xml:space="preserve">LOC SAN MICHELE </t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7473,65 +7473,6 @@
         <v>0</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>Da seguire</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>22973</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>FIDENZA</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOC SAN MICHELE </t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>IACOPINI ALESSANDRA</t>
-        </is>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>11051</v>
+        <v>11611</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8757</v>
+        <v>9183</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6733</v>
+        <v>7144</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>579</v>
+        <v>608</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>869</v>
+        <v>927</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>726</v>
+        <v>756</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,17 +877,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02151</t>
+          <t>56817</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AGRATE BRIANZA</t>
+          <t>SARONNO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA MATTEOTTI 133</t>
+          <t>VIA ROMA ANGOLO VIA IMOLA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,35 +897,35 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>523</v>
+        <v>575</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>427</v>
+        <v>95</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>261</v>
+        <v>347</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>775</v>
+        <v>443</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>56817</t>
+          <t>02151</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SARONNO</t>
+          <t>AGRATE BRIANZA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA ANGOLO VIA IMOLA</t>
+          <t>VIA MATTEOTTI 133</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>87</v>
+        <v>438</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>333</v>
+        <v>270</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>420</v>
+        <v>813</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,52 +1019,52 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO EMANUELE 5</t>
+          <t>STRADA PROV.LE N.23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>231</v>
+        <v>423</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.LE N.23</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>443</v>
+        <v>367</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>396</v>
+        <v>249</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SS VARESINA KM 13+770</t>
+          <t>CORSO ALESSANDRIA 494</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>71</v>
+        <v>199</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO ALESSANDRIA 494</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>328</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>189</v>
+        <v>76</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 135</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>VIA TORINO 135</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>148</v>
+        <v>212</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS20 KM12+230</t>
+          <t>VIA MILANO 10</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>85</v>
+        <v>244</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>24</v>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 10</t>
+          <t>SS20 KM12+230</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>228</v>
+        <v>88</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 70</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>36</v>
+        <v>219</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>227</v>
+        <v>426</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA S.VITO SILVESTRO</t>
+          <t>VIA EMILIA, 70</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>337</v>
+        <v>263</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02848</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>CROSIO DELLA VALLE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>VIA RISORGIMENTO 12</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>63</v>
+        <v>246</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>232</v>
+        <v>366</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02848</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CROSIO DELLA VALLE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA RISORGIMENTO 12</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>183</v>
+        <v>308</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>12</v>
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>43</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,52 +2376,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVARA</t>
+          <t>VIA MARTIRI DI CERVAROLO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2429,33 +2429,37 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>CARCIONE PARIDE</t>
+        </is>
+      </c>
       <c r="F38" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>396</v>
+        <v>180</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>182</v>
+        <v>59</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>606</v>
+        <v>99</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2466,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DI CERVAROLO</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2484,37 +2488,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>CARCIONE PARIDE</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="12" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>174</v>
+        <v>417</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>95</v>
+        <v>640</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2549,35 +2549,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2608,31 +2608,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2643,17 +2643,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2663,56 +2663,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>219</v>
+        <v>90</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PIACENTINA</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2722,56 +2722,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SS 36 KM 30+083</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2781,56 +2781,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEI MILLE</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2840,56 +2840,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2899,35 +2899,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2962,31 +2962,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>31</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2997,17 +2997,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3017,56 +3017,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA LIGURIA 1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3076,35 +3076,35 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3115,17 +3115,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA LIGURIA 1</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3135,35 +3135,35 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3174,17 +3174,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3194,56 +3194,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>243</v>
-      </c>
       <c r="N51" s="12" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3253,35 +3253,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>103</v>
+        <v>257</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3292,17 +3292,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3312,39 +3312,39 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3375,31 +3375,31 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3410,17 +3410,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3430,35 +3430,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="I55" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3489,56 +3489,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K56" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L56" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3548,35 +3548,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3587,17 +3587,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3607,56 +3607,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="K58" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L58" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="L58" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M58" s="12" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3666,56 +3666,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3725,56 +3725,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>57</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3784,56 +3784,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3843,39 +3843,39 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3906,31 +3906,31 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 18+000</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3961,35 +3961,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K64" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="M64" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="N64" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="N64" s="12" t="n">
-        <v>34</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4000,17 +4000,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4020,39 +4020,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4083,52 +4083,52 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4138,39 +4138,39 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4201,52 +4201,52 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4256,56 +4256,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4315,39 +4315,39 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>49</v>
@@ -4396,13 +4396,13 @@
         <v>20</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4413,17 +4413,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4433,56 +4433,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4492,56 +4492,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G73" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="K73" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4551,56 +4551,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>S.S. 10</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4610,39 +4610,39 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>63</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4673,19 +4673,19 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>10</v>
@@ -4694,10 +4694,10 @@
         <v>20</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4708,17 +4708,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>S.P 59 KM 6.500 VIGEVANESE</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4728,35 +4728,35 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4767,17 +4767,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4787,56 +4787,56 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>C.SO VERCELLI, 138</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4846,35 +4846,35 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4885,17 +4885,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TANG.TO SUD-RACC. DROSSO</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4905,56 +4905,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4964,56 +4964,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" s="12" t="n">
         <v>49</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I81" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>43</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>TANG.TO SUD-RACC. DROSSO</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5023,35 +5023,35 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -5062,17 +5062,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5082,56 +5082,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="N83" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5141,35 +5141,35 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -5180,17 +5180,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5200,56 +5200,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
         <v>45</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5259,56 +5259,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H86" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="J86" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="K86" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA MURAT 14</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5318,56 +5318,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
         <v>43</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5377,35 +5377,35 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
         <v>43</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5416,17 +5416,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5436,56 +5436,56 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5495,56 +5495,56 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G90" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J90" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H90" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="K90" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="N90" s="12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5554,56 +5554,56 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5613,35 +5613,35 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H92" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5652,17 +5652,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5672,35 +5672,35 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5711,17 +5711,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L94" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="N94" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="M94" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="N94" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5770,17 +5770,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5790,39 +5790,39 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5853,10 +5853,10 @@
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>17</v>
@@ -5871,10 +5871,10 @@
         <v>6</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N96" s="12" t="n">
         <v>7</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>0</v>
@@ -5924,40 +5924,40 @@
         <v>0</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L97" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N97" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5967,35 +5967,35 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="N98" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -6006,17 +6006,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6026,35 +6026,35 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H99" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I99" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="N99" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>31</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H100" s="12" t="n">
         <v>26</v>
@@ -6110,7 +6110,7 @@
         <v>11</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N100" s="12" t="n">
         <v>2</v>
@@ -6124,17 +6124,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6144,56 +6144,56 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J101" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G101" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="K101" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6203,20 +6203,20 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="J102" s="12" t="n">
         <v>24</v>
@@ -6225,17 +6225,17 @@
         <v>6</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6266,31 +6266,31 @@
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K103" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N103" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -6301,17 +6301,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,23 +6321,23 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K104" s="12" t="n">
         <v>8</v>
@@ -6346,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6360,17 +6360,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6380,56 +6380,56 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N105" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M105" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6439,35 +6439,35 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="H106" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N106" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="N106" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6478,17 +6478,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6498,56 +6498,56 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6557,56 +6557,56 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G108" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H108" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H108" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="I108" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6616,56 +6616,56 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K109" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L109" s="12" t="n">
+      <c r="M109" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="N109" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M109" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6679,31 +6679,31 @@
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N110" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6738,19 +6738,19 @@
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K111" s="12" t="n">
         <v>3</v>
@@ -6759,10 +6759,10 @@
         <v>0</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N111" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>16</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H112" s="12" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N113" s="12" t="n">
         <v>2</v>
@@ -6891,17 +6891,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>S.S.336 PER MALPENSA  KM.8+500</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6911,56 +6911,56 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K114" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>S.S.336 PER MALPENSA  KM.8+500</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6970,17 +6970,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I115" s="12" t="n">
         <v>0</v>
@@ -6989,13 +6989,13 @@
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I117" s="12" t="n">
         <v>0</v>
@@ -7113,14 +7113,14 @@
         <v>0</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N117" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N118" s="12" t="n">
         <v>0</v>
@@ -7186,17 +7186,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7210,52 +7210,52 @@
         </is>
       </c>
       <c r="F119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7269,19 +7269,19 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K120" s="12" t="n">
         <v>0</v>
@@ -7290,14 +7290,14 @@
         <v>0</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>11611</v>
+        <v>12170</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9183</v>
+        <v>9604</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>7144</v>
+        <v>7518</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>927</v>
+        <v>988</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>756</v>
+        <v>800</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>575</v>
+        <v>626</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>143</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>117</v>
@@ -1158,7 +1158,7 @@
         <v>59</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>172</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CORSO ALESSANDRIA 494</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>257</v>
+        <v>132</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SS VARESINA KM 13+770</t>
+          <t>CORSO ALESSANDRIA 494</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>279</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>354</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>328</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>120</v>
-      </c>
       <c r="J19" s="12" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
+        <v>267</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>242</v>
-      </c>
       <c r="H21" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>71</v>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SS33KM24+86 - SEMPIONE</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>306</v>
+        <v>451</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>24</v>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS20 KM12+230</t>
+          <t>SS33KM24+86 - SEMPIONE</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>192</v>
+        <v>362</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>88</v>
+        <v>322</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA S.VITO SILVESTRO</t>
+          <t>SS20 KM12+230</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>351</v>
+        <v>210</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>219</v>
+        <v>71</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>426</v>
+        <v>94</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2081,52 +2081,52 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>366</v>
+        <v>207</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>192</v>
+        <v>388</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>20</v>
@@ -2270,16 +2270,16 @@
         <v>20</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>12</v>
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>36</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVARA</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2488,54 +2488,58 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>DELLERBA ALBERTO</t>
+        </is>
+      </c>
       <c r="F39" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>417</v>
+        <v>145</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>640</v>
+        <v>53</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2543,37 +2547,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>GUERRA GIUSEPPE</t>
-        </is>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>159</v>
+        <v>443</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>24</v>
+        <v>674</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>281</v>
+        <v>161</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2584,17 +2584,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VL EUROPA</t>
+          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2604,39 +2604,39 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2667,31 +2667,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2702,17 +2702,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2722,56 +2722,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PIACENTINA</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2781,39 +2781,39 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2844,31 +2844,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2903,52 +2903,52 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>LORENTEGGIO 0239</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G47" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="J47" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2997,17 +2997,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3017,35 +3017,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>111</v>
+        <v>233</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>37</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>16</v>
@@ -3101,10 +3101,10 @@
         <v>35</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3115,17 +3115,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3135,56 +3135,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>252</v>
+        <v>98</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3194,56 +3194,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>87</v>
+        <v>274</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3253,35 +3253,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3316,28 +3316,28 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>10</v>
@@ -3351,17 +3351,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SS 11 KM 25+300</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3371,35 +3371,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L54" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="M54" s="12" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3410,17 +3410,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>SS 11 KM 25+300</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3430,35 +3430,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3493,52 +3493,52 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3548,56 +3548,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,31 +3611,31 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="K58" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="N58" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>39</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3646,17 +3646,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3666,35 +3666,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H59" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="N59" s="12" t="n">
         <v>30</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J59" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K59" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3705,17 +3705,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3725,35 +3725,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3764,17 +3764,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3784,35 +3784,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3823,17 +3823,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3843,56 +3843,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3902,56 +3902,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>64</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L63" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3961,35 +3961,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G64" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>60</v>
-      </c>
       <c r="K64" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L64" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>194</v>
-      </c>
       <c r="N64" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4000,17 +4000,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 18+000</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4020,35 +4020,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4059,17 +4059,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4079,56 +4079,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4138,56 +4138,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="K67" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L67" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="M67" s="12" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>STR. STATALE 31 KM 22+335</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4197,35 +4197,35 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>59</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>STR. STATALE 31 KM 22+335</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4256,56 +4256,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4315,56 +4315,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K70" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L70" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L70" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="M70" s="12" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA CISA LIGURE 10</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4374,56 +4374,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4433,35 +4433,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4472,17 +4472,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4492,35 +4492,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>60</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4531,17 +4531,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIA CISA LIGURE 10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4551,39 +4551,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L74" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>206</v>
+        <v>90</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4614,31 +4614,31 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>63</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L75" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4649,17 +4649,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,52 +4673,52 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I76" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L76" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J76" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M76" s="12" t="n">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,35 +4732,35 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4794,13 +4794,13 @@
         <v>59</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>79</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>49</v>
@@ -4812,7 +4812,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>8</v>
@@ -4826,17 +4826,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4846,35 +4846,35 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L79" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="N79" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="N79" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4885,17 +4885,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4905,56 +4905,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="H80" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="J80" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N80" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I80" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L80" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="N80" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>C.SO VERCELLI, 138</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4964,39 +4964,39 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5027,19 +5027,19 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>8</v>
@@ -5048,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>2</v>
@@ -5062,17 +5062,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5082,56 +5082,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5141,56 +5141,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H84" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>20</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>25</v>
       </c>
       <c r="L84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5200,56 +5200,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5259,56 +5259,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5318,56 +5318,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA MURAT 14</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5377,35 +5377,35 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
         <v>43</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5440,28 +5440,28 @@
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>8</v>
@@ -5475,17 +5475,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5495,35 +5495,35 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K90" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="N90" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="N90" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5534,17 +5534,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5554,56 +5554,56 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H91" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L91" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L91" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="M91" s="12" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5613,56 +5613,56 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5672,56 +5672,56 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5731,56 +5731,56 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="N94" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5790,35 +5790,35 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5829,17 +5829,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>VIA F.LLI ROSSELLI, N. 17</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5849,56 +5849,56 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G96" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I96" s="12" t="n">
+      <c r="K96" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J96" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L96" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="N96" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5908,39 +5908,39 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5971,31 +5971,31 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N98" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -6006,17 +6006,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6026,35 +6026,35 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K99" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -6065,17 +6065,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6085,39 +6085,39 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K100" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J100" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L100" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N100" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6148,19 +6148,19 @@
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>57</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K101" s="12" t="n">
         <v>6</v>
@@ -6169,10 +6169,10 @@
         <v>5</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -6207,31 +6207,31 @@
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K102" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -6266,16 +6266,16 @@
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H103" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J103" s="12" t="n">
         <v>16</v>
@@ -6284,10 +6284,10 @@
         <v>2</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="N103" s="12" t="n">
         <v>5</v>
@@ -6301,17 +6301,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,35 +6321,35 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>35</v>
+        <v>204</v>
       </c>
       <c r="J104" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6384,19 +6384,19 @@
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K105" s="12" t="n">
         <v>7</v>
@@ -6405,10 +6405,10 @@
         <v>0</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6419,17 +6419,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>198</v>
+        <v>36</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K106" s="12" t="n">
         <v>8</v>
@@ -6464,10 +6464,10 @@
         <v>0</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6478,17 +6478,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6502,31 +6502,31 @@
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N107" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="N107" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6537,17 +6537,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6557,56 +6557,56 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M108" s="12" t="n">
         <v>55</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6616,56 +6616,56 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="N109" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6675,56 +6675,56 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K110" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="M110" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N110" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M110" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6734,56 +6734,56 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K111" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N111" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="N111" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6793,35 +6793,35 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H112" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J112" s="12" t="n">
+      <c r="M112" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N112" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="K112" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L112" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M112" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N112" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6856,19 +6856,19 @@
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G113" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I113" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K113" s="12" t="n">
         <v>6</v>
@@ -6877,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N113" s="12" t="n">
         <v>2</v>
@@ -6891,17 +6891,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6911,39 +6911,39 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G114" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H114" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="I114" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K114" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L114" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N114" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M114" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N114" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0</v>
@@ -6992,17 +6992,17 @@
         <v>6</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N117" s="12" t="n">
         <v>2</v>
@@ -7154,13 +7154,13 @@
         <v>6</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H118" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J118" s="12" t="n">
         <v>6</v>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N118" s="12" t="n">
         <v>0</v>
@@ -7186,17 +7186,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01416</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SERRAVALLE SCRIVIA</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7210,52 +7210,52 @@
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>01416</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SERRAVALLE SCRIVIA</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>SS 35/BIS KM. 0+600 C/O OUTLET</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7269,52 +7269,52 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J120" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K120" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>02667</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>VIA MANFREDI 74</t>
+          <t>SS PER REGGIO EMILIA, 36/A</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7324,56 +7324,56 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>02667</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>VIA SS468</t>
+          <t>VIA MANFREDI 74 IMP. 2667</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
@@ -7408,14 +7408,14 @@
         <v>0</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOC SAN MICHELE </t>
+          <t>SP SORAGNA</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="12" t="n">
         <v>0</v>
@@ -7467,14 +7467,14 @@
         <v>0</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N123" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12170</v>
+        <v>12896</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9604</v>
+        <v>10173</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>7518</v>
+        <v>8096</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>988</v>
+        <v>1042</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>800</v>
+        <v>842</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>626</v>
+        <v>697</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>852</v>
+        <v>907</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>02862</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>CASSANO MAGNAGO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO EMANUELE 5</t>
+          <t>VIA MARIO ALBINO BONICALZA 127</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>388</v>
+        <v>508</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02862</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASSANO MAGNAGO</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA MARIO ALBINO BONICALZA 127</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,35 +1192,35 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>467</v>
+        <v>383</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SS VARESINA KM 13+770</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>356</v>
+        <v>240</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>271</v>
+        <v>173</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO ALESSANDRIA 494</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>354</v>
+        <v>419</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>268</v>
+        <v>116</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>222</v>
+        <v>276</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02308</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LEGNANO</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIALE L. CADORNA 60</t>
+          <t>CORSO ALESSANDRIA 494</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>151</v>
+        <v>279</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>477</v>
+        <v>226</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI, 9</t>
+          <t>VIA TORINO 135</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>419</v>
+        <v>234</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02308</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>LEGNANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>VIALE L. CADORNA 60</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>214</v>
+        <v>420</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>162</v>
+        <v>500</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 135</t>
+          <t>VIA GRAMSCI, 9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>72</v>
+        <v>245</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>219</v>
+        <v>451</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>204</v>
-      </c>
       <c r="H25" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>24</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>54</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>207</v>
+        <v>284</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>318</v>
+        <v>413</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06416</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DI CERVAROLO</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>191</v>
+        <v>66</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>06416</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VL EUROPA</t>
+          <t>VIA MARTIRI DI CERVAROLO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>326</v>
+        <v>131</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVARA</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2547,37 +2547,41 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>DELLERBA ALBERTO</t>
+        </is>
+      </c>
       <c r="F40" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>443</v>
+        <v>157</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>674</v>
+        <v>59</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>161</v>
+        <v>358</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2608,31 +2612,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2643,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2663,39 +2667,39 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2726,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2761,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2779,37 +2783,33 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>CERRI SARA</t>
-        </is>
-      </c>
+      <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="12" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>163</v>
+        <v>463</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>147</v>
+        <v>706</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2820,17 +2820,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS 36 KM 30+083</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2840,56 +2840,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEI MILLE</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2899,56 +2899,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>55313</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ORIGGIO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS 233 KM 20+110</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>121</v>
+        <v>247</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2997,17 +2997,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>55313</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>ORIGGIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LORENTEGGIO 0239</t>
+          <t>SS 233 KM 20+110</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3017,35 +3017,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3139,16 +3139,16 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>80</v>
@@ -3157,17 +3157,17 @@
         <v>35</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>9</v>
@@ -3233,17 +3233,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3253,35 +3253,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="H52" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="I52" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>87</v>
-      </c>
       <c r="J52" s="12" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3292,17 +3292,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3312,56 +3312,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>186</v>
+      </c>
+      <c r="H54" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="I54" s="12" t="n">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>146</v>
+        <v>287</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3434,28 +3434,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>13</v>
@@ -3469,17 +3469,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3489,35 +3489,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L56" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>233</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>26</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>25</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3528,17 +3528,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3548,35 +3548,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L57" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3587,17 +3587,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,31 +3611,31 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3670,52 +3670,52 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3725,56 +3725,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3784,56 +3784,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="I61" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="K61" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L61" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="M61" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3843,56 +3843,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3902,35 +3902,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>113</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3961,35 +3961,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4000,17 +4000,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4020,35 +4020,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4059,17 +4059,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4079,35 +4079,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4118,17 +4118,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4138,56 +4138,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M67" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H67" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>127</v>
-      </c>
       <c r="N67" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 18+000</t>
+          <t>STR. STATALE 31 KM 22+335</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4197,35 +4197,35 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>STR. STATALE 31 KM 22+335</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4256,56 +4256,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4315,35 +4315,35 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="K70" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L70" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J70" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M70" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="N70" s="12" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4378,52 +4378,52 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L71" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4433,56 +4433,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4492,39 +4492,39 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4555,31 +4555,31 @@
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L74" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4590,17 +4590,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>8</v>
@@ -4649,17 +4649,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>S.S. 10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4669,35 +4669,35 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G76" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="I76" s="12" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4708,17 +4708,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4728,56 +4728,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K77" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="N77" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L77" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="N77" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>S.P 59 KM 6.500 VIGEVANESE</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4787,39 +4787,39 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4850,28 +4850,28 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>18</v>
@@ -4909,28 +4909,28 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>7</v>
@@ -4944,17 +4944,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>TANG.TO SUD-RACC. DROSSO</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4964,35 +4964,35 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -5003,17 +5003,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>TANG.TO SUD-RACC. DROSSO</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5023,56 +5023,56 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5082,39 +5082,39 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5145,28 +5145,28 @@
         </is>
       </c>
       <c r="F84" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G84" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G84" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="H84" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>21</v>
@@ -5180,17 +5180,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5200,56 +5200,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5259,56 +5259,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="K86" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="N86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L86" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M86" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="N86" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5318,56 +5318,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5377,23 +5377,23 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>10</v>
@@ -5402,31 +5402,31 @@
         <v>10</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5436,35 +5436,35 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H89" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K89" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I89" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K89" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L89" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>VIA MURAT 14</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5499,31 +5499,31 @@
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="N90" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5534,17 +5534,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5558,52 +5558,52 @@
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="H91" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="N91" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L91" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M91" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="N91" s="12" t="n">
-        <v>37</v>
-      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5613,56 +5613,56 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5672,56 +5672,56 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M93" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J93" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>VIA F.LLI ROSSELLI, N. 17</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="N94" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5770,17 +5770,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5790,35 +5790,35 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5829,17 +5829,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5849,56 +5849,56 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="N96" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5908,39 +5908,39 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H97" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5971,19 +5971,19 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K98" s="12" t="n">
         <v>9</v>
@@ -5992,7 +5992,7 @@
         <v>6</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N98" s="12" t="n">
         <v>4</v>
@@ -6006,17 +6006,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6026,56 +6026,56 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6085,56 +6085,56 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K100" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="N100" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6144,39 +6144,39 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K101" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6207,19 +6207,19 @@
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K102" s="12" t="n">
         <v>6</v>
@@ -6228,10 +6228,10 @@
         <v>7</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -6242,17 +6242,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6262,56 +6262,56 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I103" s="12" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N103" s="12" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,35 +6321,35 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6360,17 +6360,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6380,56 +6380,56 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="H105" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G105" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="I105" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6439,39 +6439,39 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F106" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J106" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="G106" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="K106" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6502,35 +6502,35 @@
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L107" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -6561,19 +6561,19 @@
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K108" s="12" t="n">
         <v>12</v>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H109" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K109" s="12" t="n">
         <v>4</v>
@@ -6641,10 +6641,10 @@
         <v>4</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N109" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6679,19 +6679,19 @@
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H110" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K110" s="12" t="n">
         <v>5</v>
@@ -6700,14 +6700,14 @@
         <v>3</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N110" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6738,35 +6738,35 @@
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L111" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N111" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -6797,19 +6797,19 @@
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K112" s="12" t="n">
         <v>3</v>
@@ -6818,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N112" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6871,13 +6871,13 @@
         <v>17</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N113" s="12" t="n">
         <v>2</v>
@@ -6918,7 +6918,7 @@
         <v>16</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H114" s="12" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G115" s="12" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K115" s="12" t="n">
         <v>6</v>
@@ -6995,7 +6995,7 @@
         <v>7</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N115" s="12" t="n">
         <v>0</v>
@@ -7009,17 +7009,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
+          <t>SS PER REGGIO EMILIA, 36/A</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7033,31 +7033,31 @@
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N116" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -7068,17 +7068,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I117" s="12" t="n">
         <v>0</v>
@@ -7107,16 +7107,16 @@
         <v>9</v>
       </c>
       <c r="K117" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N117" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="L117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N117" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -7127,17 +7127,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>DUE GIUGNO</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7147,56 +7147,56 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="N118" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>01409</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>NOVI LIGURE</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>VIA MAZZINI 56</t>
+          <t>DUE GIUGNO</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7206,39 +7206,39 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>DELUGAS NADIA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="N119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7269,28 +7269,28 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J120" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K120" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K120" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="L120" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N120" s="12" t="n">
         <v>0</v>
@@ -7304,17 +7304,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>FIDENZA</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>SS PER REGGIO EMILIA, 36/A</t>
+          <t>SP SORAGNA</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7328,19 +7328,19 @@
         </is>
       </c>
       <c r="F121" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N121" s="12" t="n">
         <v>1</v>
@@ -7363,17 +7363,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>02667</t>
+          <t>01409</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>NOVI LIGURE</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>VIA MANFREDI 74 IMP. 2667</t>
+          <t>VIA MAZZINI 56</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -7383,11 +7383,11 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>DELUGAS NADIA</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>0</v>
@@ -7399,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K122" s="12" t="n">
         <v>0</v>
@@ -7408,31 +7408,31 @@
         <v>0</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N122" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>02667</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>FIDENZA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>SP SORAGNA</t>
+          <t>VIA MANFREDI 74 IMP. 2667</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F123" s="12" t="n">
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="12" t="n">
         <v>0</v>
@@ -7467,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123" s="12" t="n">
         <v>1</v>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12896</v>
+        <v>13449</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10173</v>
+        <v>10607</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>8096</v>
+        <v>8515</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>577</v>
+        <v>613</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1042</v>
+        <v>1095</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>118</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>907</v>
+        <v>958</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>00415</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GARBAGNATE MILANESE</t>
+          <t>PIEDIMULERA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SS VARESINA KM 13+770</t>
+          <t>VIA ROMA 157</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>383</v>
+        <v>244</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>298</v>
+        <v>180</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>00415</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PIEDIMULERA</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA 157</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>240</v>
+        <v>435</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>GARBAGNATE MILANESE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO EMANUELE 5</t>
+          <t>SS VARESINA KM 13+770</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>00209</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>CUNEO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO ALESSANDRIA 494</t>
+          <t>VIA TORINO 135</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>369</v>
+        <v>293</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="K20" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="L20" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="L20" s="12" t="n">
-        <v>61</v>
-      </c>
       <c r="M20" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00209</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CUNEO</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 135</t>
+          <t>VIA GRAMSCI, 9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>234</v>
+        <v>466</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA GRAMSCI, 9</t>
+          <t>CORSO ALESSANDRIA 494</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>285</v>
+        <v>380</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>245</v>
+        <v>295</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>451</v>
+        <v>226</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIACENZA</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FARNESIANA 151</t>
+          <t>VIA MILANO 10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>441</v>
+        <v>297</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>PIACENZA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 10</t>
+          <t>VIA FARNESIANA 151</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>223</v>
+        <v>334</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>280</v>
+        <v>459</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02261</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE OLONA</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SS33KM24+86 - SEMPIONE</t>
+          <t>VIA EMILIA, 70</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>347</v>
+        <v>282</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00718</t>
+          <t>02261</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CARIGNANO</t>
+          <t>SAN VITTORE OLONA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SS20 KM12+230</t>
+          <t>SS33KM24+86 - SEMPIONE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>233</v>
+        <v>407</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>00718</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>CARIGNANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 70</t>
+          <t>SS20 KM12+230</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>298</v>
+        <v>234</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>267</v>
+        <v>104</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K31" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>64</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>223</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>59</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>59</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>00407</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>OMEGNA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VAI CAMILLO CAMPARI</t>
+          <t>VIA IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>320</v>
+        <v>58</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>402</v>
+        <v>107</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>00407</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>OMEGNA</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA IV NOVEMBRE</t>
+          <t>VAI CAMILLO CAMPARI</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>52</v>
+        <v>331</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>104</v>
+        <v>421</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2494,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>10</v>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIVOLI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VL EUROPA</t>
+          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>RIVOLI</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L42" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="M42" s="12" t="n">
-        <v>272</v>
+        <v>135</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PIACENTINA</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,39 +2726,39 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>134</v>
+        <v>288</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2788,13 +2788,13 @@
         <v>130</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>182</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>102</v>
@@ -2844,31 +2844,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2879,17 +2879,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS 36 KM 30+083</t>
+          <t>LORENTEGGIO 0239</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2899,35 +2899,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2938,17 +2938,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>LORENTEGGIO 0239</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3021,31 +3021,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3056,17 +3056,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA LIGURIA 1</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3076,35 +3076,35 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3115,17 +3115,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTEROSA 6</t>
+          <t>VIA LIGURIA 1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3135,56 +3135,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3194,56 +3194,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>295</v>
+        <v>166</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3253,32 +3253,32 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>139</v>
+        <v>298</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>10</v>
@@ -3292,17 +3292,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3312,56 +3312,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA MONTEROSA 6</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>186</v>
+        <v>92</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3434,28 +3434,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>13</v>
@@ -3469,17 +3469,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3489,56 +3489,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="G56" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="12" t="n">
-        <v>152</v>
-      </c>
       <c r="H56" s="12" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3548,39 +3548,39 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3611,31 +3611,31 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3646,17 +3646,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3666,56 +3666,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3725,39 +3725,39 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>86</v>
+        <v>248</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3788,31 +3788,31 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3823,17 +3823,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3843,56 +3843,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="K62" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L62" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L62" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M62" s="12" t="n">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3902,56 +3902,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3961,56 +3961,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>116</v>
+        <v>226</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>STR. STATALE 31 KM 22+335</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4020,35 +4020,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4059,17 +4059,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4079,56 +4079,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4138,56 +4138,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>STR. STATALE 31 KM 22+335</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4197,56 +4197,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4256,35 +4256,35 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4295,17 +4295,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4315,35 +4315,35 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4354,17 +4354,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4374,56 +4374,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
         <v>74</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4433,56 +4433,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4492,35 +4492,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4531,17 +4531,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA CISA LIGURE 10</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4551,35 +4551,35 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="J74" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M74" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K74" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="N74" s="12" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4590,17 +4590,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>01480</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>ASTI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>S.S. 10</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4610,35 +4610,35 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I75" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N75" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="N75" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4649,17 +4649,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01480</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ASTI</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10</t>
+          <t>VIA CISA LIGURE 10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4669,35 +4669,35 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4708,17 +4708,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CORSICO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>S.P 59 KM 6.500 VIGEVANESE</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4728,56 +4728,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4787,35 +4787,35 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4826,17 +4826,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>52469</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>CORSICO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>S.P 59 KM 6.500 VIGEVANESE</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4846,56 +4846,56 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K79" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>203</v>
+      </c>
+      <c r="N79" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L79" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="N79" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4905,56 +4905,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TANG.TO SUD-RACC. DROSSO</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4964,56 +4964,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="L81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N81" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M81" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="N81" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,31 +5027,31 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K82" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="N82" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -5062,17 +5062,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5082,56 +5082,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>C.SO VERCELLI, 138</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5141,56 +5141,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>TANG.TO SUD-RACC. DROSSO</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5200,35 +5200,35 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5239,17 +5239,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5259,56 +5259,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5318,56 +5318,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>214</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="N87" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5377,39 +5377,39 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5440,28 +5440,28 @@
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L89" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>41</v>
@@ -5475,17 +5475,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5495,56 +5495,56 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G90" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K90" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L90" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M90" s="12" t="n">
-        <v>168</v>
-      </c>
       <c r="N90" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5554,56 +5554,56 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="H91" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J91" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>53</v>
-      </c>
       <c r="K91" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>91</v>
+        <v>177</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5613,35 +5613,35 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="H92" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G92" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="I92" s="12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5652,17 +5652,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5672,39 +5672,39 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>2</v>
@@ -5753,10 +5753,10 @@
         <v>8</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N94" s="12" t="n">
         <v>9</v>
@@ -5770,17 +5770,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5790,35 +5790,35 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5829,17 +5829,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>VIA F.LLI ROSSELLI, N. 17</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5849,56 +5849,56 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K96" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L96" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L96" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M96" s="12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="N96" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5908,35 +5908,35 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
         <v>40</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5947,17 +5947,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5971,52 +5971,52 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K98" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N98" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6026,56 +6026,56 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I99" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L99" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J99" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M99" s="12" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6085,35 +6085,35 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="12" t="n">
         <v>35</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>23</v>
       </c>
       <c r="K100" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="N100" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -6124,17 +6124,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6144,35 +6144,35 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J101" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="K101" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -6183,17 +6183,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6203,35 +6203,35 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="J102" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K102" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="N102" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -6266,31 +6266,31 @@
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I103" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J103" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N103" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -6301,17 +6301,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,35 +6321,35 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="H104" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6360,17 +6360,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>01481</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA D'ASTI</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>REGIONE PIEVE N.47</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6380,35 +6380,35 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G105" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M105" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H105" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="N105" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6419,17 +6419,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>01481</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>VILLAFRANCA D'ASTI</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>REGIONE PIEVE N.47</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6439,56 +6439,56 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6498,39 +6498,39 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6561,31 +6561,31 @@
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G109" s="12" t="n">
         <v>51</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K109" s="12" t="n">
         <v>4</v>
@@ -6641,7 +6641,7 @@
         <v>4</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N109" s="12" t="n">
         <v>13</v>
@@ -6655,17 +6655,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6679,31 +6679,31 @@
         </is>
       </c>
       <c r="F110" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G110" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K110" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="N110" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6714,17 +6714,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6738,28 +6738,28 @@
         </is>
       </c>
       <c r="F111" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="K111" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="N111" s="12" t="n">
         <v>3</v>
@@ -6797,19 +6797,19 @@
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I112" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K112" s="12" t="n">
         <v>3</v>
@@ -6818,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N112" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6832,17 +6832,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>GALVANI 34</t>
+          <t>SS PER REGGIO EMILIA, 36/A</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6852,32 +6852,32 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="N113" s="12" t="n">
         <v>2</v>
@@ -6891,17 +6891,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>GALVANI 34</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6911,56 +6911,56 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I114" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>S.S.336 PER MALPENSA  KM.8+500</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6970,56 +6970,56 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G115" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H115" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I115" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J115" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K115" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>SS PER REGGIO EMILIA, 36/A</t>
+          <t>S.S.336 PER MALPENSA  KM.8+500</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7029,35 +7029,35 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K116" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="N116" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -7092,22 +7092,22 @@
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L117" s="12" t="n">
         <v>1</v>
@@ -7151,19 +7151,19 @@
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K118" s="12" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N118" s="12" t="n">
         <v>2</v>
@@ -7219,7 +7219,7 @@
         <v>23</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J119" s="12" t="n">
         <v>6</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
@@ -7272,13 +7272,13 @@
         <v>5</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J120" s="12" t="n">
         <v>4</v>
@@ -7290,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N120" s="12" t="n">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         <v>4</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" s="12" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13449</v>
+        <v>14190</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10607</v>
+        <v>11213</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>8515</v>
+        <v>9047</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>662</v>
+        <v>697</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1095</v>
+        <v>1149</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>874</v>
+        <v>927</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>485</v>
+        <v>514</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>77</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>156</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>958</v>
+        <v>1018</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>517</v>
+        <v>561</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1553,13 +1553,13 @@
         <v>284</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>211</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>227</v>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="K24" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="L24" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="M24" s="12" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>23</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02838</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VARESE</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA S.VITO SILVESTRO</t>
+          <t>VIA EMILIA, 70</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>415</v>
+        <v>311</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>281</v>
+        <v>56</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>509</v>
+        <v>296</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02838</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>VARESE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 70</t>
+          <t>VIA S.VITO SILVESTRO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>308</v>
+        <v>450</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>50</v>
+        <v>318</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>282</v>
+        <v>540</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>56</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>217</v>
+        <v>359</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>353</v>
+        <v>455</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>345</v>
+        <v>242</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>429</v>
+        <v>365</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN GIOVANNI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PIACENTINA</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CASTEL SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VIA EMILIA PIACENTINA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H43" s="12" t="n">
+        <v>181</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>109</v>
-      </c>
       <c r="K43" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>288</v>
+        <v>139</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>00352</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BORGOMANERO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA NOVARA</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2783,54 +2783,58 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>RAVA CLAUDIO</t>
+        </is>
+      </c>
       <c r="F44" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>476</v>
+        <v>152</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>738</v>
+        <v>87</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>7</v>
+        <v>161</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>00352</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>BORGOMANERO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEI MILLE</t>
+          <t>VIA NOVARA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2838,41 +2842,37 @@
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>RAVA CLAUDIO</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>140</v>
+        <v>506</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>83</v>
+        <v>781</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2903,31 +2903,31 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>198</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>61</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2962,31 +2962,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3021,31 +3021,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3056,17 +3056,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>02874</t>
+          <t>55557</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>OLGIATE OLONA</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA FAGNANO OLONA  30</t>
+          <t>VIA TRAVERSETOLO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3076,39 +3076,39 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>313</v>
+        <v>175</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3174,17 +3174,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>55557</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA TRAVERSETOLO</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3194,56 +3194,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>97</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>166</v>
+        <v>316</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>02874</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>OLGIATE OLONA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA FAGNANO OLONA  30</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3253,32 +3253,32 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>10</v>
@@ -3292,17 +3292,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>02824</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CORNAREDO</t>
+          <t>MALNATE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI</t>
+          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3312,35 +3312,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>142</v>
+        <v>266</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3375,31 +3375,31 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3410,17 +3410,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CORNAREDO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 11 KM 25+300</t>
+          <t>VIA GARIBALDI</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3430,56 +3430,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>97</v>
+        <v>228</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CASALE MONFERRATO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>STR PROV PER VALENZA 4/B</t>
+          <t>SS 11 KM 25+300</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3489,56 +3489,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>VIGNADUZZO EDI</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L56" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M56" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="N56" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="M56" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>63</v>
-      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>02872</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>LONATE POZZOLO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+          <t>S.S.527 KM 45 664</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3548,56 +3548,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>CICCARELLI AUGUSTO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>73</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>02872</t>
+          <t>02400</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>LONATE POZZOLO</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S.527 KM 45 664</t>
+          <t>PACE</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3607,35 +3607,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>QUATTROCCHI FILIPPO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="I58" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G58" s="12" t="n">
-        <v>156</v>
-      </c>
-      <c r="H58" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="J58" s="12" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>72</v>
+        <v>263</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3646,17 +3646,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>02824</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>MALNATE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA KENNEDY ANG. VIA PROVINCIALE SNC</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3666,56 +3666,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>CICCARELLI AUGUSTO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>02400</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>CASALE MONFERRATO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>PACE</t>
+          <t>STR PROV PER VALENZA 4/B</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3725,39 +3725,39 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>QUATTROCCHI FILIPPO</t>
+          <t>VIGNADUZZO EDI</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>248</v>
+        <v>102</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3788,31 +3788,31 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3823,17 +3823,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>02705</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PODENZANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3843,56 +3843,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>GIURICIN ANTONIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3902,35 +3902,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3941,17 +3941,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3961,35 +3961,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4024,19 +4024,19 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>13</v>
@@ -4045,10 +4045,10 @@
         <v>9</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4059,17 +4059,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>00116</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>VARALLO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>VIA M. T. ROSSI  17/3</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4079,56 +4079,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>02705</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>PODENZANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIA PAPA GIOVANNI XXIII</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4138,56 +4138,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIURICIN ANTONIO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>C.SO TRIESTE, 54B</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4197,56 +4197,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>00116</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>VARALLO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA M. T. ROSSI  17/3</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4256,56 +4256,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="K69" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M69" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="N69" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L69" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N69" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MESERO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>C.SO TRIESTE, 54B</t>
+          <t>SP 31 KM 12+45</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4315,56 +4315,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>RECCHIA ALESSANDRO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>00494</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MESERO</t>
+          <t>CAMERI</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>SP 31 KM 12+45</t>
+          <t>VIALE MARCONI 64</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4374,56 +4374,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>RECCHIA ALESSANDRO</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L71" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>00494</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CAMERI</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIALE MARCONI 64</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4433,56 +4433,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>59</v>
-      </c>
       <c r="K72" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4492,56 +4492,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4551,39 +4551,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="G74" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G74" s="12" t="n">
-        <v>112</v>
-      </c>
       <c r="H74" s="12" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4614,31 +4614,31 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4649,17 +4649,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>06403</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>GUASTALLA</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA CISA LIGURE 10</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4669,56 +4669,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I76" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M76" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="N76" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J76" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="N76" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,52 +4732,52 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>29</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>06403</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>GUASTALLA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>VIA CISA LIGURE 10</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4787,39 +4787,39 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4850,31 +4850,31 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4885,17 +4885,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4905,39 +4905,39 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4968,28 +4968,28 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L81" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>3</v>
@@ -5003,17 +5003,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PARMA</t>
+          <t>NOVARA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVA 109 A</t>
+          <t>C.SO VERCELLI, 138</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5023,56 +5023,56 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="L82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="N82" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M82" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>NOVARA</t>
+          <t>MONTECCHIO EMILIA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>C.SO VERCELLI, 138</t>
+          <t>S.P PER REGGIO EMILIA 34</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5082,56 +5082,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>06446</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MONTECCHIO EMILIA</t>
+          <t>REGGIO NELL'EMILIA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>S.P PER REGGIO EMILIA 34</t>
+          <t>VIA GORIZIA, 25</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5141,56 +5141,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>CARCIONE PARIDE</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G84" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>131</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>91</v>
-      </c>
       <c r="N84" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>00974</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>BEINASCO</t>
+          <t>PARMA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>TANG.TO SUD-RACC. DROSSO</t>
+          <t>VIA MANTOVA 109 A</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5200,56 +5200,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>RAMPONE ROBERTO</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>06446</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>REGGIO NELL'EMILIA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VIA GORIZIA, 25</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5259,35 +5259,35 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CARCIONE PARIDE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5298,17 +5298,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>00974</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>BEINASCO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>TANG.TO SUD-RACC. DROSSO</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5318,56 +5318,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>RAMPONE ROBERTO</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>00460</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>TRECATE</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5377,56 +5377,56 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5440,31 +5440,31 @@
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5475,17 +5475,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>00460</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>TRECATE</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5495,56 +5495,56 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="N90" s="12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5554,35 +5554,35 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J91" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G91" s="12" t="n">
-        <v>99</v>
-      </c>
-      <c r="H91" s="12" t="n">
+      <c r="K91" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I91" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L91" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5593,17 +5593,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5613,35 +5613,35 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="H92" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J92" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="I92" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="K92" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5652,17 +5652,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5672,35 +5672,35 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5735,28 +5735,28 @@
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K94" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L94" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N94" s="12" t="n">
         <v>9</v>
@@ -5770,17 +5770,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5790,56 +5790,56 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5849,56 +5849,56 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K96" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N96" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>VIA F.LLI ROSSELLI, N. 17</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5908,56 +5908,56 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I97" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K97" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L97" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L97" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M97" s="12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5971,52 +5971,52 @@
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K98" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L98" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L98" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M98" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="N98" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6030,31 +6030,31 @@
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N99" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -6065,17 +6065,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6085,35 +6085,35 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="N100" s="12" t="n">
         <v>35</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -6124,17 +6124,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>00452</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>STRESA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>SS 33</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6144,56 +6144,56 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>VERBANIA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>CORSO EUROPA</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6203,35 +6203,35 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>SVANINI EDOARDO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H102" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="N102" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="N102" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -6242,17 +6242,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6262,35 +6262,35 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G103" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="I103" s="12" t="n">
+      <c r="K103" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L103" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J103" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="K103" s="12" t="n">
+      <c r="M103" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L103" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>102</v>
-      </c>
       <c r="N103" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -6301,17 +6301,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>00452</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>STRESA</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>SS 33</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6321,56 +6321,56 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="J104" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K104" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>VERBANIA</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>CORSO EUROPA</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6380,35 +6380,35 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>SVANINI EDOARDO</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="I105" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J105" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6443,31 +6443,31 @@
         </is>
       </c>
       <c r="F106" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J106" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K106" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6478,17 +6478,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6498,56 +6498,56 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I107" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J107" s="12" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6557,56 +6557,56 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J108" s="12" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K108" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>SANT'ILARIO D'ENZA</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARI 38</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6616,39 +6616,39 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>IACONA GIOVANNI</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I109" s="12" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="J109" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="N109" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -6679,22 +6679,22 @@
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J110" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K110" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L110" s="12" t="n">
         <v>1</v>
@@ -6714,17 +6714,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>53490</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>SANT'ILARIO D'ENZA</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>VIA FERRARI 38</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6734,39 +6734,39 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>IACONA GIOVANNI</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J111" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G111" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I111" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K111" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="N111" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6797,19 +6797,19 @@
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I112" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J112" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K112" s="12" t="n">
         <v>3</v>
@@ -6832,17 +6832,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>52106</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CORREGGIO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>SS PER REGGIO EMILIA, 36/A</t>
+          <t>GALVANI 34</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6852,35 +6852,35 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="N113" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6891,17 +6891,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CORREGGIO</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GALVANI 34</t>
+          <t>SS PER REGGIO EMILIA, 36/A</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6911,35 +6911,35 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I114" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>16</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H115" s="12" t="n">
         <v>0</v>
@@ -7009,17 +7009,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>02925</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>CARDANO AL CAMPO</t>
+          <t>BERCETO</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>S.S.336 PER MALPENSA  KM.8+500</t>
+          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>SALVINELLI LUCA</t>
+          <t>IACOPINI ALESSANDRA</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
@@ -7039,25 +7039,25 @@
         <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K116" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="N116" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -7068,17 +7068,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>02925</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>BERCETO</t>
+          <t>CARDANO AL CAMPO</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>SS 308 KM. 20+148 LOC. GHIARE</t>
+          <t>S.S.336 PER MALPENSA  KM.8+500</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7088,17 +7088,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>IACOPINI ALESSANDRA</t>
+          <t>SALVINELLI LUCA</t>
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I117" s="12" t="n">
         <v>0</v>
@@ -7107,37 +7107,37 @@
         <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>SANTHIÀ</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>DUE GIUGNO</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7147,56 +7147,56 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BIANCHI ENRICO</t>
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="J118" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K118" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="N118" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SANTHIÀ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>DUE GIUGNO</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7206,39 +7206,39 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>BIANCHI ENRICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I119" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J119" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="N119" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -7269,19 +7269,19 @@
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J120" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K120" s="12" t="n">
         <v>2</v>
@@ -7290,10 +7290,10 @@
         <v>1</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N120" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" s="12" t="n">
         <v>0</v>
@@ -7349,14 +7349,14 @@
         <v>0</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N121" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N122" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -7446,31 +7446,31 @@
         </is>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N123" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Nadir Abdel.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>113</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>14190</v>
+        <v>14934</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>11213</v>
+        <v>11799</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>9047</v>
+        <v>9697</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>633</v>
+        <v>668</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1149</v>
+        <v>1204</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>927</v>
+        <v>977</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>735</v>
+        <v>764</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>647</v>
+        <v>689</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>1018</v>
+        <v>1074</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>55</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
  